--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21210" windowHeight="11430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24855" windowHeight="11640"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$4</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$5</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C3" s="1">
-        <v>15598</v>
+        <v>15560</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -405,6 +405,17 @@
       </c>
       <c r="C4" s="1">
         <v>7333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>20200408</v>
+      </c>
+      <c r="B5" s="1">
+        <v>559</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10498</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24855" windowHeight="11640"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21345" windowHeight="11745"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$5</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$6</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C4" s="1">
-        <v>7333</v>
+        <v>7331</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,21 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="C5" s="1">
-        <v>10498</v>
+        <v>9942</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>20200409</v>
+      </c>
+      <c r="B6" s="1">
+        <v>482</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5974</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21345" windowHeight="11745"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21180" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$6</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$7</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C3" s="1">
-        <v>15560</v>
+        <v>15555</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C5" s="1">
-        <v>9942</v>
+        <v>9891</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -427,6 +427,17 @@
       </c>
       <c r="C6" s="1">
         <v>5974</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>20200414</v>
+      </c>
+      <c r="B7" s="1">
+        <v>261</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3218</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21180" windowHeight="11655"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21750" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$7</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$8</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="C3" s="1">
-        <v>15555</v>
+        <v>15538</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C4" s="1">
-        <v>7331</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C5" s="1">
-        <v>9891</v>
+        <v>9888</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -438,6 +438,17 @@
       </c>
       <c r="C7" s="1">
         <v>3218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>20200415</v>
+      </c>
+      <c r="B8" s="1">
+        <v>429</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5710</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21750" windowHeight="11760"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="13260"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$8</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$9</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C3" s="1">
-        <v>15538</v>
+        <v>15534</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C4" s="1">
-        <v>7329</v>
+        <v>7291</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -423,10 +423,10 @@
         <v>20200409</v>
       </c>
       <c r="B6" s="1">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C6" s="1">
-        <v>5974</v>
+        <v>5973</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -434,10 +434,10 @@
         <v>20200414</v>
       </c>
       <c r="B7" s="1">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C7" s="1">
-        <v>3218</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -449,6 +449,17 @@
       </c>
       <c r="C8" s="1">
         <v>5710</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>20200416</v>
+      </c>
+      <c r="B9" s="1">
+        <v>228</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2474</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="13260"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22350" windowHeight="13155"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$9</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$10</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C3" s="1">
-        <v>15534</v>
+        <v>15532</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C5" s="1">
-        <v>9888</v>
+        <v>9885</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -423,10 +423,10 @@
         <v>20200409</v>
       </c>
       <c r="B6" s="1">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C6" s="1">
-        <v>5973</v>
+        <v>5916</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -445,7 +445,7 @@
         <v>20200415</v>
       </c>
       <c r="B8" s="1">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C8" s="1">
         <v>5710</v>
@@ -460,6 +460,17 @@
       </c>
       <c r="C9" s="1">
         <v>2474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>20200417</v>
+      </c>
+      <c r="B10" s="1">
+        <v>294</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1736</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$10</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$11</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C3" s="1">
-        <v>15532</v>
+        <v>15513</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C4" s="1">
-        <v>7291</v>
+        <v>7286</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C5" s="1">
-        <v>9885</v>
+        <v>9819</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -423,10 +423,10 @@
         <v>20200409</v>
       </c>
       <c r="B6" s="1">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C6" s="1">
-        <v>5916</v>
+        <v>5906</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -471,6 +471,17 @@
       </c>
       <c r="C10" s="1">
         <v>1736</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>20200420</v>
+      </c>
+      <c r="B11" s="1">
+        <v>142</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1499</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22350" windowHeight="13155"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11640"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$11</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$13</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C3" s="1">
-        <v>15513</v>
+        <v>15510</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C4" s="1">
-        <v>7286</v>
+        <v>7255</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C5" s="1">
-        <v>9819</v>
+        <v>9793</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -423,10 +423,10 @@
         <v>20200409</v>
       </c>
       <c r="B6" s="1">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C6" s="1">
-        <v>5906</v>
+        <v>5902</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -434,10 +434,10 @@
         <v>20200414</v>
       </c>
       <c r="B7" s="1">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C7" s="1">
-        <v>3104</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -445,10 +445,10 @@
         <v>20200415</v>
       </c>
       <c r="B8" s="1">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C8" s="1">
-        <v>5710</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -456,10 +456,10 @@
         <v>20200416</v>
       </c>
       <c r="B9" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" s="1">
-        <v>2474</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -467,10 +467,10 @@
         <v>20200417</v>
       </c>
       <c r="B10" s="1">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C10" s="1">
-        <v>1736</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -478,10 +478,32 @@
         <v>20200420</v>
       </c>
       <c r="B11" s="1">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C11" s="1">
-        <v>1499</v>
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>20200421</v>
+      </c>
+      <c r="B12" s="1">
+        <v>391</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>20200422</v>
+      </c>
+      <c r="B13" s="1">
+        <v>318</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2934</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11640"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23025" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$13</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$14</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="C3" s="1">
-        <v>15510</v>
+        <v>15506</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="C4" s="1">
-        <v>7255</v>
+        <v>7162</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C5" s="1">
-        <v>9793</v>
+        <v>9791</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -423,10 +423,10 @@
         <v>20200409</v>
       </c>
       <c r="B6" s="1">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C6" s="1">
-        <v>5902</v>
+        <v>5895</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -434,10 +434,10 @@
         <v>20200414</v>
       </c>
       <c r="B7" s="1">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C7" s="1">
-        <v>3071</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -445,10 +445,10 @@
         <v>20200415</v>
       </c>
       <c r="B8" s="1">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C8" s="1">
-        <v>5703</v>
+        <v>5566</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -467,10 +467,10 @@
         <v>20200417</v>
       </c>
       <c r="B10" s="1">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C10" s="1">
-        <v>1731</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -489,10 +489,10 @@
         <v>20200421</v>
       </c>
       <c r="B12" s="1">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C12" s="1">
-        <v>4316</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -500,10 +500,21 @@
         <v>20200422</v>
       </c>
       <c r="B13" s="1">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C13" s="1">
-        <v>2934</v>
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>20200423</v>
+      </c>
+      <c r="B14" s="1">
+        <v>375</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3368</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$14</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C4" s="1">
-        <v>7162</v>
+        <v>7161</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -511,10 +511,21 @@
         <v>20200423</v>
       </c>
       <c r="B14" s="1">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C14" s="1">
-        <v>3368</v>
+        <v>3429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>20200424</v>
+      </c>
+      <c r="B15" s="1">
+        <v>166</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2447</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$15</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$16</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="C3" s="1">
-        <v>15506</v>
+        <v>15493</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C4" s="1">
-        <v>7161</v>
+        <v>7159</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -423,10 +423,10 @@
         <v>20200409</v>
       </c>
       <c r="B6" s="1">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C6" s="1">
-        <v>5895</v>
+        <v>5878</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -467,10 +467,10 @@
         <v>20200417</v>
       </c>
       <c r="B10" s="1">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C10" s="1">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -478,10 +478,10 @@
         <v>20200420</v>
       </c>
       <c r="B11" s="1">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="1">
-        <v>1501</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -511,10 +511,10 @@
         <v>20200423</v>
       </c>
       <c r="B14" s="1">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C14" s="1">
-        <v>3429</v>
+        <v>3428</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -522,10 +522,21 @@
         <v>20200424</v>
       </c>
       <c r="B15" s="1">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="1">
-        <v>2447</v>
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>20200427</v>
+      </c>
+      <c r="B16" s="1">
+        <v>210</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1968</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$16</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$17</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C3" s="1">
-        <v>15493</v>
+        <v>15467</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -412,10 +412,10 @@
         <v>20200408</v>
       </c>
       <c r="B5" s="1">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C5" s="1">
-        <v>9791</v>
+        <v>9769</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -456,10 +456,10 @@
         <v>20200416</v>
       </c>
       <c r="B9" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1">
-        <v>2471</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -500,10 +500,10 @@
         <v>20200422</v>
       </c>
       <c r="B13" s="1">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C13" s="1">
-        <v>2933</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -511,10 +511,10 @@
         <v>20200423</v>
       </c>
       <c r="B14" s="1">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C14" s="1">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -522,10 +522,10 @@
         <v>20200424</v>
       </c>
       <c r="B15" s="1">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="1">
-        <v>2427</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -533,10 +533,21 @@
         <v>20200427</v>
       </c>
       <c r="B16" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C16" s="1">
-        <v>1968</v>
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>20200428</v>
+      </c>
+      <c r="B17" s="1">
+        <v>222</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1775</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$17</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$18</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -401,10 +401,10 @@
         <v>20200407</v>
       </c>
       <c r="B4" s="1">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C4" s="1">
-        <v>7159</v>
+        <v>7154</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -445,10 +445,10 @@
         <v>20200415</v>
       </c>
       <c r="B8" s="1">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C8" s="1">
-        <v>5566</v>
+        <v>5564</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -489,10 +489,10 @@
         <v>20200421</v>
       </c>
       <c r="B12" s="1">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C12" s="1">
-        <v>4283</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -500,10 +500,10 @@
         <v>20200422</v>
       </c>
       <c r="B13" s="1">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C13" s="1">
-        <v>2915</v>
+        <v>2914</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -511,10 +511,10 @@
         <v>20200423</v>
       </c>
       <c r="B14" s="1">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C14" s="1">
-        <v>3427</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -522,10 +522,10 @@
         <v>20200424</v>
       </c>
       <c r="B15" s="1">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="1">
-        <v>2397</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -548,6 +548,17 @@
       </c>
       <c r="C17" s="1">
         <v>1775</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>20200429</v>
+      </c>
+      <c r="B18" s="1">
+        <v>167</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1472</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23025" windowHeight="12045"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19575" windowHeight="11490"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$18</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$19</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -359,7 +359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -390,10 +390,10 @@
         <v>20200406</v>
       </c>
       <c r="B3" s="3">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="C3" s="1">
-        <v>15467</v>
+        <v>14907</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -445,10 +445,10 @@
         <v>20200415</v>
       </c>
       <c r="B8" s="1">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C8" s="1">
-        <v>5564</v>
+        <v>5560</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -467,10 +467,10 @@
         <v>20200417</v>
       </c>
       <c r="B10" s="1">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C10" s="1">
-        <v>1717</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -511,10 +511,10 @@
         <v>20200423</v>
       </c>
       <c r="B14" s="1">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C14" s="1">
-        <v>3408</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -533,10 +533,10 @@
         <v>20200427</v>
       </c>
       <c r="B16" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C16" s="1">
-        <v>1965</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -558,7 +558,18 @@
         <v>167</v>
       </c>
       <c r="C18" s="1">
-        <v>1472</v>
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>20200430</v>
+      </c>
+      <c r="B19" s="1">
+        <v>228</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3168</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kt.ktzh.ch\vd_w19\VD_W19\VDW19Users\B167AN1\System\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\kt.ktzh.ch\vd_w19\VD_W19\VDW19Users\b167an1\System\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19575" windowHeight="11490"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11130"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$19</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$30</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Metriken</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Kurzarbeit/Schlechtwetter - Tag Entscheid</t>
+  </si>
+  <si>
+    <t>20200301 - 20200405</t>
   </si>
 </sst>
 </file>
@@ -73,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -359,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -367,7 +371,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -378,199 +382,376 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>17920</v>
+      </c>
+      <c r="C3" s="1">
+        <v>182618</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>20200406</v>
       </c>
-      <c r="B3" s="3">
-        <v>1129</v>
-      </c>
-      <c r="C3" s="1">
-        <v>14907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="B4" s="3">
+        <v>19008</v>
+      </c>
+      <c r="C4" s="1">
+        <v>197115</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>20200407</v>
       </c>
-      <c r="B4" s="1">
-        <v>746</v>
-      </c>
-      <c r="C4" s="1">
-        <v>7154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="B5" s="3">
+        <v>19744</v>
+      </c>
+      <c r="C5" s="1">
+        <v>203951</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <v>20200408</v>
       </c>
-      <c r="B5" s="1">
-        <v>525</v>
-      </c>
-      <c r="C5" s="1">
-        <v>9769</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="B6" s="3">
+        <v>20264</v>
+      </c>
+      <c r="C6" s="1">
+        <v>213613</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <v>20200409</v>
       </c>
-      <c r="B6" s="1">
-        <v>475</v>
-      </c>
-      <c r="C6" s="1">
-        <v>5878</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="B7" s="1">
+        <v>20729</v>
+      </c>
+      <c r="C7" s="1">
+        <v>219108</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <v>20200414</v>
       </c>
-      <c r="B7" s="1">
-        <v>257</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3064</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="B8" s="1">
+        <v>20984</v>
+      </c>
+      <c r="C8" s="1">
+        <v>222165</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <v>20200415</v>
       </c>
-      <c r="B8" s="1">
-        <v>422</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5560</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="B9" s="1">
+        <v>21404</v>
+      </c>
+      <c r="C9" s="1">
+        <v>227708</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>20200416</v>
       </c>
-      <c r="B9" s="1">
-        <v>226</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="B10" s="1">
+        <v>21629</v>
+      </c>
+      <c r="C10" s="1">
+        <v>229396</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
         <v>20200417</v>
       </c>
-      <c r="B10" s="1">
-        <v>290</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="B11" s="1">
+        <v>21914</v>
+      </c>
+      <c r="C11" s="1">
+        <v>231100</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>20200420</v>
       </c>
-      <c r="B11" s="1">
-        <v>146</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1486</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+      <c r="B12" s="1">
+        <v>22059</v>
+      </c>
+      <c r="C12" s="1">
+        <v>232561</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>20200421</v>
       </c>
-      <c r="B12" s="1">
-        <v>389</v>
-      </c>
-      <c r="C12" s="1">
-        <v>4282</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="B13" s="1">
+        <v>22444</v>
+      </c>
+      <c r="C13" s="1">
+        <v>236780</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
         <v>20200422</v>
       </c>
-      <c r="B13" s="1">
-        <v>312</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2914</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+      <c r="B14" s="1">
+        <v>22749</v>
+      </c>
+      <c r="C14" s="1">
+        <v>239675</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
         <v>20200423</v>
       </c>
-      <c r="B14" s="1">
-        <v>373</v>
-      </c>
-      <c r="C14" s="1">
-        <v>3404</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+      <c r="B15" s="1">
+        <v>23111</v>
+      </c>
+      <c r="C15" s="1">
+        <v>243024</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
         <v>20200424</v>
       </c>
-      <c r="B15" s="1">
-        <v>163</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2396</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+      <c r="B16" s="1">
+        <v>23266</v>
+      </c>
+      <c r="C16" s="1">
+        <v>245384</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
         <v>20200427</v>
       </c>
-      <c r="B16" s="1">
-        <v>207</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+      <c r="B17" s="1">
+        <v>23470</v>
+      </c>
+      <c r="C17" s="1">
+        <v>247286</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
         <v>20200428</v>
       </c>
-      <c r="B17" s="1">
-        <v>222</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+      <c r="B18" s="1">
+        <v>23687</v>
+      </c>
+      <c r="C18" s="1">
+        <v>249048</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
         <v>20200429</v>
       </c>
-      <c r="B18" s="1">
-        <v>167</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+      <c r="B19" s="1">
+        <v>23848</v>
+      </c>
+      <c r="C19" s="1">
+        <v>250460</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
         <v>20200430</v>
       </c>
-      <c r="B19" s="1">
-        <v>228</v>
-      </c>
-      <c r="C19" s="1">
-        <v>3168</v>
-      </c>
+      <c r="B20" s="1">
+        <v>24072</v>
+      </c>
+      <c r="C20" s="1">
+        <v>253611</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20200504</v>
+      </c>
+      <c r="B21" s="1">
+        <v>24713</v>
+      </c>
+      <c r="C21" s="1">
+        <v>265626</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>20200505</v>
+      </c>
+      <c r="B22" s="1">
+        <v>25573</v>
+      </c>
+      <c r="C22" s="1">
+        <v>279459</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>20200506</v>
+      </c>
+      <c r="B23" s="1">
+        <v>26411</v>
+      </c>
+      <c r="C23" s="1">
+        <v>291666</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>20200507</v>
+      </c>
+      <c r="B24" s="3">
+        <v>27551</v>
+      </c>
+      <c r="C24" s="1">
+        <v>305870</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>20200508</v>
+      </c>
+      <c r="B25" s="3">
+        <v>28468</v>
+      </c>
+      <c r="C25" s="1">
+        <v>315768</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>20200511</v>
+      </c>
+      <c r="B26" s="1">
+        <v>29406</v>
+      </c>
+      <c r="C26" s="1">
+        <v>330803</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>20200512</v>
+      </c>
+      <c r="B27" s="1">
+        <v>29955</v>
+      </c>
+      <c r="C27" s="1">
+        <v>338761</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>20200513</v>
+      </c>
+      <c r="B28" s="1">
+        <v>30525</v>
+      </c>
+      <c r="C28" s="1">
+        <v>347215</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>20200514</v>
+      </c>
+      <c r="B29" s="1">
+        <v>31062</v>
+      </c>
+      <c r="C29" s="1">
+        <v>352502</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>20200515</v>
+      </c>
+      <c r="B30" s="1">
+        <v>31510</v>
+      </c>
+      <c r="C30" s="1">
+        <v>367466</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="13305"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$31</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$32</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -41,7 +41,7 @@
     <t>Kurzarbeit/Schlechtwetter - Tag Entscheid</t>
   </si>
   <si>
-    <t>20200301 - 20200405</t>
+    <t>20200301 20200405</t>
   </si>
 </sst>
 </file>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>17578</v>
+        <v>17055</v>
       </c>
       <c r="C3" s="1">
-        <v>177884</v>
+        <v>169431</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>18661</v>
+        <v>18134</v>
       </c>
       <c r="C4" s="1">
-        <v>192359</v>
+        <v>183889</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>19397</v>
+        <v>18868</v>
       </c>
       <c r="C5" s="1">
-        <v>199195</v>
+        <v>190719</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>19917</v>
+        <v>19388</v>
       </c>
       <c r="C6" s="1">
-        <v>208857</v>
+        <v>200381</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -445,11 +445,11 @@
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
-      <c r="B7" s="1">
-        <v>20382</v>
+      <c r="B7" s="3">
+        <v>19852</v>
       </c>
       <c r="C7" s="1">
-        <v>214352</v>
+        <v>205872</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="1">
-        <v>20637</v>
+        <v>20107</v>
       </c>
       <c r="C8" s="1">
-        <v>217409</v>
+        <v>208929</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>21057</v>
+        <v>20527</v>
       </c>
       <c r="C9" s="1">
-        <v>222952</v>
+        <v>214472</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>21282</v>
+        <v>20752</v>
       </c>
       <c r="C10" s="1">
-        <v>224640</v>
+        <v>216160</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>21567</v>
+        <v>21037</v>
       </c>
       <c r="C11" s="1">
-        <v>226344</v>
+        <v>217864</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>21711</v>
+        <v>21181</v>
       </c>
       <c r="C12" s="1">
-        <v>227798</v>
+        <v>219318</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>22096</v>
+        <v>21565</v>
       </c>
       <c r="C13" s="1">
-        <v>232017</v>
+        <v>223536</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>22401</v>
+        <v>21870</v>
       </c>
       <c r="C14" s="1">
-        <v>234912</v>
+        <v>226431</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>22762</v>
+        <v>22230</v>
       </c>
       <c r="C15" s="1">
-        <v>238259</v>
+        <v>229777</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>22916</v>
+        <v>22384</v>
       </c>
       <c r="C16" s="1">
-        <v>240618</v>
+        <v>232136</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>23120</v>
+        <v>22588</v>
       </c>
       <c r="C17" s="1">
-        <v>242520</v>
+        <v>234038</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>23337</v>
+        <v>22805</v>
       </c>
       <c r="C18" s="1">
-        <v>244282</v>
+        <v>235800</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>23497</v>
+        <v>22963</v>
       </c>
       <c r="C19" s="1">
-        <v>245690</v>
+        <v>237202</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>23721</v>
+        <v>23187</v>
       </c>
       <c r="C20" s="1">
-        <v>248841</v>
+        <v>240353</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>24360</v>
+        <v>23826</v>
       </c>
       <c r="C21" s="1">
-        <v>260729</v>
+        <v>252241</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>25220</v>
+        <v>24686</v>
       </c>
       <c r="C22" s="1">
-        <v>274562</v>
+        <v>266074</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>26057</v>
+        <v>25521</v>
       </c>
       <c r="C23" s="1">
-        <v>286728</v>
+        <v>278238</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>27196</v>
+        <v>26659</v>
       </c>
       <c r="C24" s="1">
-        <v>300930</v>
+        <v>292439</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>28113</v>
+        <v>27576</v>
       </c>
       <c r="C25" s="1">
-        <v>310828</v>
+        <v>302337</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -692,11 +692,11 @@
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
-      <c r="B26" s="1">
-        <v>29051</v>
+      <c r="B26" s="3">
+        <v>28514</v>
       </c>
       <c r="C26" s="1">
-        <v>325863</v>
+        <v>317372</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="1">
-        <v>29600</v>
+        <v>29061</v>
       </c>
       <c r="C27" s="1">
-        <v>333821</v>
+        <v>325319</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>30169</v>
+        <v>29629</v>
       </c>
       <c r="C28" s="1">
-        <v>342273</v>
+        <v>333770</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>30706</v>
+        <v>30165</v>
       </c>
       <c r="C29" s="1">
-        <v>347560</v>
+        <v>339055</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>31153</v>
+        <v>30612</v>
       </c>
       <c r="C30" s="1">
-        <v>362509</v>
+        <v>354004</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,13 +758,26 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>31572</v>
+        <v>31031</v>
       </c>
       <c r="C31" s="1">
-        <v>368156</v>
+        <v>359651</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>20200519</v>
+      </c>
+      <c r="B32" s="1">
+        <v>31638</v>
+      </c>
+      <c r="C32" s="1">
+        <v>368369</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$32</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$33</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -41,7 +41,7 @@
     <t>Kurzarbeit/Schlechtwetter - Tag Entscheid</t>
   </si>
   <si>
-    <t>20200301 20200405</t>
+    <t>20200301 - 20200405</t>
   </si>
 </sst>
 </file>
@@ -76,12 +76,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -363,7 +362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -371,7 +370,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,402 +381,353 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>17055</v>
+        <v>16655</v>
       </c>
       <c r="C3" s="1">
-        <v>169431</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>164332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>18134</v>
+        <v>17733</v>
       </c>
       <c r="C4" s="1">
-        <v>183889</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>178788</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>18868</v>
+        <v>18467</v>
       </c>
       <c r="C5" s="1">
-        <v>190719</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>185618</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>19388</v>
+        <v>18987</v>
       </c>
       <c r="C6" s="1">
-        <v>200381</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>195280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>19852</v>
+        <v>19450</v>
       </c>
       <c r="C7" s="1">
-        <v>205872</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>200768</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="1">
-        <v>20107</v>
+        <v>19705</v>
       </c>
       <c r="C8" s="1">
-        <v>208929</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>203825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>20527</v>
+        <v>20125</v>
       </c>
       <c r="C9" s="1">
-        <v>214472</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>209368</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>20752</v>
+        <v>20350</v>
       </c>
       <c r="C10" s="1">
-        <v>216160</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>211056</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>21037</v>
+        <v>20635</v>
       </c>
       <c r="C11" s="1">
-        <v>217864</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>212760</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>21181</v>
+        <v>20779</v>
       </c>
       <c r="C12" s="1">
-        <v>219318</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>214214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>21565</v>
+        <v>21163</v>
       </c>
       <c r="C13" s="1">
-        <v>223536</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>218432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>21870</v>
+        <v>21468</v>
       </c>
       <c r="C14" s="1">
-        <v>226431</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>221327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>22230</v>
+        <v>21826</v>
       </c>
       <c r="C15" s="1">
-        <v>229777</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>224669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>22384</v>
+        <v>21978</v>
       </c>
       <c r="C16" s="1">
-        <v>232136</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>227026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>22588</v>
+        <v>22181</v>
       </c>
       <c r="C17" s="1">
-        <v>234038</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>228927</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>22805</v>
+        <v>22398</v>
       </c>
       <c r="C18" s="1">
-        <v>235800</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>230689</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>22963</v>
+        <v>22555</v>
       </c>
       <c r="C19" s="1">
-        <v>237202</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>232090</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>23187</v>
+        <v>22775</v>
       </c>
       <c r="C20" s="1">
-        <v>240353</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>235233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>23826</v>
+        <v>23413</v>
       </c>
       <c r="C21" s="1">
-        <v>252241</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>247119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>24686</v>
+        <v>24272</v>
       </c>
       <c r="C22" s="1">
-        <v>266074</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>260951</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>25521</v>
+        <v>25107</v>
       </c>
       <c r="C23" s="1">
-        <v>278238</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>273115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>26659</v>
+        <v>26245</v>
       </c>
       <c r="C24" s="1">
-        <v>292439</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>287316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>27576</v>
+        <v>27161</v>
       </c>
       <c r="C25" s="1">
-        <v>302337</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>297209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>28514</v>
+        <v>28099</v>
       </c>
       <c r="C26" s="1">
-        <v>317372</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>312244</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="1">
-        <v>29061</v>
+        <v>28646</v>
       </c>
       <c r="C27" s="1">
-        <v>325319</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>320191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>29629</v>
+        <v>29214</v>
       </c>
       <c r="C28" s="1">
-        <v>333770</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>328642</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>30165</v>
+        <v>29749</v>
       </c>
       <c r="C29" s="1">
-        <v>339055</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>333878</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>30612</v>
+        <v>30194</v>
       </c>
       <c r="C30" s="1">
-        <v>354004</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>348794</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>31031</v>
+        <v>30612</v>
       </c>
       <c r="C31" s="1">
-        <v>359651</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>354440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>31638</v>
+        <v>31219</v>
       </c>
       <c r="C32" s="1">
-        <v>368369</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
+        <v>363158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>20200520</v>
+      </c>
+      <c r="B33" s="1">
+        <v>31702</v>
+      </c>
+      <c r="C33" s="1">
+        <v>368726</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$33</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$34</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -362,7 +362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -393,10 +393,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>16655</v>
+        <v>16241</v>
       </c>
       <c r="C3" s="1">
-        <v>164332</v>
+        <v>159898</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -404,10 +404,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>17733</v>
+        <v>17319</v>
       </c>
       <c r="C4" s="1">
-        <v>178788</v>
+        <v>174354</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -415,10 +415,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>18467</v>
+        <v>18053</v>
       </c>
       <c r="C5" s="1">
-        <v>185618</v>
+        <v>181184</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -426,10 +426,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>18987</v>
+        <v>18573</v>
       </c>
       <c r="C6" s="1">
-        <v>195280</v>
+        <v>190846</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -437,10 +437,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>19450</v>
+        <v>19036</v>
       </c>
       <c r="C7" s="1">
-        <v>200768</v>
+        <v>196334</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -448,10 +448,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="1">
-        <v>19705</v>
+        <v>19291</v>
       </c>
       <c r="C8" s="1">
-        <v>203825</v>
+        <v>199391</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -459,10 +459,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>20125</v>
+        <v>19711</v>
       </c>
       <c r="C9" s="1">
-        <v>209368</v>
+        <v>204934</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -470,10 +470,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>20350</v>
+        <v>19936</v>
       </c>
       <c r="C10" s="1">
-        <v>211056</v>
+        <v>206622</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -481,10 +481,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>20635</v>
+        <v>20221</v>
       </c>
       <c r="C11" s="1">
-        <v>212760</v>
+        <v>208326</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -492,10 +492,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>20779</v>
+        <v>20365</v>
       </c>
       <c r="C12" s="1">
-        <v>214214</v>
+        <v>209780</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -503,10 +503,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>21163</v>
+        <v>20749</v>
       </c>
       <c r="C13" s="1">
-        <v>218432</v>
+        <v>213998</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -514,10 +514,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>21468</v>
+        <v>21053</v>
       </c>
       <c r="C14" s="1">
-        <v>221327</v>
+        <v>216888</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -525,10 +525,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>21826</v>
+        <v>21411</v>
       </c>
       <c r="C15" s="1">
-        <v>224669</v>
+        <v>220230</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -536,10 +536,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>21978</v>
+        <v>21563</v>
       </c>
       <c r="C16" s="1">
-        <v>227026</v>
+        <v>222587</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -547,10 +547,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>22181</v>
+        <v>21766</v>
       </c>
       <c r="C17" s="1">
-        <v>228927</v>
+        <v>224488</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -558,10 +558,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>22398</v>
+        <v>21983</v>
       </c>
       <c r="C18" s="1">
-        <v>230689</v>
+        <v>226250</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -569,10 +569,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>22555</v>
+        <v>22140</v>
       </c>
       <c r="C19" s="1">
-        <v>232090</v>
+        <v>227651</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -580,10 +580,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>22775</v>
+        <v>22360</v>
       </c>
       <c r="C20" s="1">
-        <v>235233</v>
+        <v>230794</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -591,10 +591,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>23413</v>
+        <v>22998</v>
       </c>
       <c r="C21" s="1">
-        <v>247119</v>
+        <v>242680</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -602,10 +602,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>24272</v>
+        <v>23857</v>
       </c>
       <c r="C22" s="1">
-        <v>260951</v>
+        <v>256512</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -613,10 +613,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>25107</v>
+        <v>24691</v>
       </c>
       <c r="C23" s="1">
-        <v>273115</v>
+        <v>268673</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -624,10 +624,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>26245</v>
+        <v>25828</v>
       </c>
       <c r="C24" s="1">
-        <v>287316</v>
+        <v>282870</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -635,10 +635,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>27161</v>
+        <v>26744</v>
       </c>
       <c r="C25" s="1">
-        <v>297209</v>
+        <v>292763</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -646,10 +646,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>28099</v>
+        <v>27681</v>
       </c>
       <c r="C26" s="1">
-        <v>312244</v>
+        <v>307792</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -657,10 +657,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="1">
-        <v>28646</v>
+        <v>28228</v>
       </c>
       <c r="C27" s="1">
-        <v>320191</v>
+        <v>315739</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -668,10 +668,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>29214</v>
+        <v>28796</v>
       </c>
       <c r="C28" s="1">
-        <v>328642</v>
+        <v>324190</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -679,10 +679,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>29749</v>
+        <v>29331</v>
       </c>
       <c r="C29" s="1">
-        <v>333878</v>
+        <v>329426</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -690,10 +690,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>30194</v>
+        <v>29776</v>
       </c>
       <c r="C30" s="1">
-        <v>348794</v>
+        <v>344342</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -701,10 +701,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>30612</v>
+        <v>30193</v>
       </c>
       <c r="C31" s="1">
-        <v>354440</v>
+        <v>349978</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -712,10 +712,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>31219</v>
+        <v>30800</v>
       </c>
       <c r="C32" s="1">
-        <v>363158</v>
+        <v>358696</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -723,10 +723,21 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>31702</v>
+        <v>31282</v>
       </c>
       <c r="C33" s="1">
-        <v>368726</v>
+        <v>364261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>20200522</v>
+      </c>
+      <c r="B34" s="1">
+        <v>31731</v>
+      </c>
+      <c r="C34" s="1">
+        <v>368923</v>
       </c>
     </row>
   </sheetData>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$34</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$35</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -76,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -362,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -370,7 +371,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -381,364 +382,441 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>16241</v>
+        <v>15960</v>
       </c>
       <c r="C3" s="1">
-        <v>159898</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>154408</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>17319</v>
+        <v>17035</v>
       </c>
       <c r="C4" s="1">
-        <v>174354</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>168855</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>18053</v>
+        <v>17768</v>
       </c>
       <c r="C5" s="1">
-        <v>181184</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>175665</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>18573</v>
+        <v>18288</v>
       </c>
       <c r="C6" s="1">
-        <v>190846</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>185327</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>19036</v>
+        <v>18751</v>
       </c>
       <c r="C7" s="1">
-        <v>196334</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>190815</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="1">
-        <v>19291</v>
+        <v>19006</v>
       </c>
       <c r="C8" s="1">
-        <v>199391</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>193872</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>19711</v>
+        <v>19426</v>
       </c>
       <c r="C9" s="1">
-        <v>204934</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>199415</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>19936</v>
+        <v>19651</v>
       </c>
       <c r="C10" s="1">
-        <v>206622</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>201103</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>20221</v>
+        <v>19935</v>
       </c>
       <c r="C11" s="1">
-        <v>208326</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>202802</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>20365</v>
+        <v>20079</v>
       </c>
       <c r="C12" s="1">
-        <v>209780</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>204256</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>20749</v>
+        <v>20463</v>
       </c>
       <c r="C13" s="1">
-        <v>213998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>208474</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>21053</v>
+        <v>20766</v>
       </c>
       <c r="C14" s="1">
-        <v>216888</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>211360</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>21411</v>
+        <v>21123</v>
       </c>
       <c r="C15" s="1">
-        <v>220230</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>214697</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>21563</v>
+        <v>21275</v>
       </c>
       <c r="C16" s="1">
-        <v>222587</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>217054</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>21766</v>
+        <v>21477</v>
       </c>
       <c r="C17" s="1">
-        <v>224488</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>218954</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>21983</v>
+        <v>21692</v>
       </c>
       <c r="C18" s="1">
-        <v>226250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>220714</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>22140</v>
+        <v>21849</v>
       </c>
       <c r="C19" s="1">
-        <v>227651</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>222115</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>22360</v>
+        <v>22069</v>
       </c>
       <c r="C20" s="1">
-        <v>230794</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>225258</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>22998</v>
+        <v>22707</v>
       </c>
       <c r="C21" s="1">
-        <v>242680</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>237144</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>23857</v>
+        <v>23566</v>
       </c>
       <c r="C22" s="1">
-        <v>256512</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>250976</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>24691</v>
+        <v>24400</v>
       </c>
       <c r="C23" s="1">
-        <v>268673</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>263137</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>25828</v>
+        <v>25537</v>
       </c>
       <c r="C24" s="1">
-        <v>282870</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>277334</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>26744</v>
+        <v>26452</v>
       </c>
       <c r="C25" s="1">
-        <v>292763</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>287226</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>27681</v>
+        <v>27389</v>
       </c>
       <c r="C26" s="1">
-        <v>307792</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>302255</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="1">
-        <v>28228</v>
+        <v>27936</v>
       </c>
       <c r="C27" s="1">
-        <v>315739</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>310202</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>28796</v>
+        <v>28504</v>
       </c>
       <c r="C28" s="1">
-        <v>324190</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>318653</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>29331</v>
+        <v>29039</v>
       </c>
       <c r="C29" s="1">
-        <v>329426</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>323889</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>29776</v>
+        <v>29484</v>
       </c>
       <c r="C30" s="1">
-        <v>344342</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>338805</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>30193</v>
+        <v>29898</v>
       </c>
       <c r="C31" s="1">
-        <v>349978</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>344434</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>30800</v>
+        <v>30504</v>
       </c>
       <c r="C32" s="1">
-        <v>358696</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>353134</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>31282</v>
+        <v>30986</v>
       </c>
       <c r="C33" s="1">
-        <v>364261</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>358699</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>31731</v>
+        <v>31434</v>
       </c>
       <c r="C34" s="1">
-        <v>368923</v>
-      </c>
+        <v>363351</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>20200525</v>
+      </c>
+      <c r="B35" s="1">
+        <v>31806</v>
+      </c>
+      <c r="C35" s="1">
+        <v>368759</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$35</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$36</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>15960</v>
+        <v>15585</v>
       </c>
       <c r="C3" s="1">
-        <v>154408</v>
+        <v>151306</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>17035</v>
+        <v>16670</v>
       </c>
       <c r="C4" s="1">
-        <v>168855</v>
+        <v>165745</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>17768</v>
+        <v>17403</v>
       </c>
       <c r="C5" s="1">
-        <v>175665</v>
+        <v>172555</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>18288</v>
+        <v>17922</v>
       </c>
       <c r="C6" s="1">
-        <v>185327</v>
+        <v>182210</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>18751</v>
+        <v>18385</v>
       </c>
       <c r="C7" s="1">
-        <v>190815</v>
+        <v>187698</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -458,11 +458,11 @@
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
-      <c r="B8" s="1">
-        <v>19006</v>
+      <c r="B8" s="3">
+        <v>18640</v>
       </c>
       <c r="C8" s="1">
-        <v>193872</v>
+        <v>190755</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>19426</v>
+        <v>19059</v>
       </c>
       <c r="C9" s="1">
-        <v>199415</v>
+        <v>196291</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>19651</v>
+        <v>19283</v>
       </c>
       <c r="C10" s="1">
-        <v>201103</v>
+        <v>197977</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>19935</v>
+        <v>19567</v>
       </c>
       <c r="C11" s="1">
-        <v>202802</v>
+        <v>199675</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>20079</v>
+        <v>19711</v>
       </c>
       <c r="C12" s="1">
-        <v>204256</v>
+        <v>201129</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>20463</v>
+        <v>20094</v>
       </c>
       <c r="C13" s="1">
-        <v>208474</v>
+        <v>205341</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>20766</v>
+        <v>20396</v>
       </c>
       <c r="C14" s="1">
-        <v>211360</v>
+        <v>208226</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>21123</v>
+        <v>20751</v>
       </c>
       <c r="C15" s="1">
-        <v>214697</v>
+        <v>211554</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>21275</v>
+        <v>20903</v>
       </c>
       <c r="C16" s="1">
-        <v>217054</v>
+        <v>213911</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>21477</v>
+        <v>21104</v>
       </c>
       <c r="C17" s="1">
-        <v>218954</v>
+        <v>215794</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>21692</v>
+        <v>21318</v>
       </c>
       <c r="C18" s="1">
-        <v>220714</v>
+        <v>217553</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>21849</v>
+        <v>21474</v>
       </c>
       <c r="C19" s="1">
-        <v>222115</v>
+        <v>218934</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>22069</v>
+        <v>21694</v>
       </c>
       <c r="C20" s="1">
-        <v>225258</v>
+        <v>222077</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>22707</v>
+        <v>22331</v>
       </c>
       <c r="C21" s="1">
-        <v>237144</v>
+        <v>233960</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>23566</v>
+        <v>23189</v>
       </c>
       <c r="C22" s="1">
-        <v>250976</v>
+        <v>247791</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>24400</v>
+        <v>24023</v>
       </c>
       <c r="C23" s="1">
-        <v>263137</v>
+        <v>259952</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>25537</v>
+        <v>25158</v>
       </c>
       <c r="C24" s="1">
-        <v>277334</v>
+        <v>274121</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>26452</v>
+        <v>26073</v>
       </c>
       <c r="C25" s="1">
-        <v>287226</v>
+        <v>284013</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>27389</v>
+        <v>27010</v>
       </c>
       <c r="C26" s="1">
-        <v>302255</v>
+        <v>299042</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -705,11 +705,11 @@
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
-      <c r="B27" s="1">
-        <v>27936</v>
+      <c r="B27" s="3">
+        <v>27557</v>
       </c>
       <c r="C27" s="1">
-        <v>310202</v>
+        <v>306989</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>28504</v>
+        <v>28124</v>
       </c>
       <c r="C28" s="1">
-        <v>318653</v>
+        <v>315438</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>29039</v>
+        <v>28656</v>
       </c>
       <c r="C29" s="1">
-        <v>323889</v>
+        <v>320667</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>29484</v>
+        <v>29101</v>
       </c>
       <c r="C30" s="1">
-        <v>338805</v>
+        <v>335583</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>29898</v>
+        <v>29515</v>
       </c>
       <c r="C31" s="1">
-        <v>344434</v>
+        <v>341212</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>30504</v>
+        <v>30120</v>
       </c>
       <c r="C32" s="1">
-        <v>353134</v>
+        <v>349910</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>30986</v>
+        <v>30602</v>
       </c>
       <c r="C33" s="1">
-        <v>358699</v>
+        <v>355475</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>31434</v>
+        <v>31050</v>
       </c>
       <c r="C34" s="1">
-        <v>363351</v>
+        <v>360127</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,13 +810,26 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>31806</v>
+        <v>31422</v>
       </c>
       <c r="C35" s="1">
-        <v>368759</v>
+        <v>365532</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>20200526</v>
+      </c>
+      <c r="B36" s="1">
+        <v>31835</v>
+      </c>
+      <c r="C36" s="1">
+        <v>368843</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$36</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$37</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -393,11 +393,11 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3">
-        <v>15585</v>
-      </c>
-      <c r="C3" s="1">
-        <v>151306</v>
+      <c r="B3" s="4">
+        <v>15330</v>
+      </c>
+      <c r="C3" s="4">
+        <v>148103</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>16670</v>
+        <v>1084</v>
       </c>
       <c r="C4" s="1">
-        <v>165745</v>
+        <v>14438</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>17403</v>
+        <v>733</v>
       </c>
       <c r="C5" s="1">
-        <v>172555</v>
+        <v>6810</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>17922</v>
+        <v>519</v>
       </c>
       <c r="C6" s="1">
-        <v>182210</v>
+        <v>9655</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>18385</v>
+        <v>462</v>
       </c>
       <c r="C7" s="1">
-        <v>187698</v>
+        <v>5485</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>18640</v>
+        <v>255</v>
       </c>
       <c r="C8" s="1">
-        <v>190755</v>
+        <v>3057</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>19059</v>
+        <v>419</v>
       </c>
       <c r="C9" s="1">
-        <v>196291</v>
+        <v>5536</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>19283</v>
+        <v>224</v>
       </c>
       <c r="C10" s="1">
-        <v>197977</v>
+        <v>1686</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>19567</v>
+        <v>284</v>
       </c>
       <c r="C11" s="1">
-        <v>199675</v>
+        <v>1698</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>19711</v>
+        <v>144</v>
       </c>
       <c r="C12" s="1">
-        <v>201129</v>
+        <v>1454</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>20094</v>
+        <v>382</v>
       </c>
       <c r="C13" s="1">
-        <v>205341</v>
+        <v>4206</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>20396</v>
+        <v>302</v>
       </c>
       <c r="C14" s="1">
-        <v>208226</v>
+        <v>2885</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>20751</v>
+        <v>355</v>
       </c>
       <c r="C15" s="1">
-        <v>211554</v>
+        <v>3328</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>20903</v>
+        <v>152</v>
       </c>
       <c r="C16" s="1">
-        <v>213911</v>
+        <v>2357</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>21104</v>
+        <v>201</v>
       </c>
       <c r="C17" s="1">
-        <v>215794</v>
+        <v>1883</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>21318</v>
+        <v>214</v>
       </c>
       <c r="C18" s="1">
-        <v>217553</v>
+        <v>1759</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>21474</v>
+        <v>156</v>
       </c>
       <c r="C19" s="1">
-        <v>218934</v>
+        <v>1381</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>21694</v>
+        <v>219</v>
       </c>
       <c r="C20" s="1">
-        <v>222077</v>
+        <v>3142</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>22331</v>
+        <v>635</v>
       </c>
       <c r="C21" s="1">
-        <v>233960</v>
+        <v>11876</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>23189</v>
+        <v>858</v>
       </c>
       <c r="C22" s="1">
-        <v>247791</v>
+        <v>13831</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>24023</v>
+        <v>834</v>
       </c>
       <c r="C23" s="1">
-        <v>259952</v>
+        <v>12161</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>25158</v>
+        <v>1134</v>
       </c>
       <c r="C24" s="1">
-        <v>274121</v>
+        <v>14168</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>26073</v>
+        <v>913</v>
       </c>
       <c r="C25" s="1">
-        <v>284013</v>
+        <v>9866</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>27010</v>
+        <v>936</v>
       </c>
       <c r="C26" s="1">
-        <v>299042</v>
+        <v>15024</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>27557</v>
+        <v>547</v>
       </c>
       <c r="C27" s="1">
-        <v>306989</v>
+        <v>7947</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>28124</v>
+        <v>567</v>
       </c>
       <c r="C28" s="1">
-        <v>315438</v>
+        <v>8449</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>28656</v>
+        <v>532</v>
       </c>
       <c r="C29" s="1">
-        <v>320667</v>
+        <v>5229</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>29101</v>
+        <v>444</v>
       </c>
       <c r="C30" s="1">
-        <v>335583</v>
+        <v>14843</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>29515</v>
+        <v>414</v>
       </c>
       <c r="C31" s="1">
-        <v>341212</v>
+        <v>5629</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>30120</v>
+        <v>605</v>
       </c>
       <c r="C32" s="1">
-        <v>349910</v>
+        <v>8698</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>30602</v>
+        <v>480</v>
       </c>
       <c r="C33" s="1">
-        <v>355475</v>
+        <v>5464</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>31050</v>
+        <v>447</v>
       </c>
       <c r="C34" s="1">
-        <v>360127</v>
+        <v>4618</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>31422</v>
+        <v>372</v>
       </c>
       <c r="C35" s="1">
-        <v>365532</v>
+        <v>5405</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,13 +823,26 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>31835</v>
+        <v>413</v>
       </c>
       <c r="C36" s="1">
-        <v>368843</v>
+        <v>3311</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>20200527</v>
+      </c>
+      <c r="B37" s="1">
+        <v>300</v>
+      </c>
+      <c r="C37" s="1">
+        <v>3589</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$37</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$36</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -393,11 +393,11 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4">
-        <v>15330</v>
-      </c>
-      <c r="C3" s="4">
-        <v>148103</v>
+      <c r="B3" s="3">
+        <v>15585</v>
+      </c>
+      <c r="C3" s="1">
+        <v>151306</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>1084</v>
+        <v>16670</v>
       </c>
       <c r="C4" s="1">
-        <v>14438</v>
+        <v>165745</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>733</v>
+        <v>17403</v>
       </c>
       <c r="C5" s="1">
-        <v>6810</v>
+        <v>172555</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>519</v>
+        <v>17922</v>
       </c>
       <c r="C6" s="1">
-        <v>9655</v>
+        <v>182210</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>462</v>
+        <v>18385</v>
       </c>
       <c r="C7" s="1">
-        <v>5485</v>
+        <v>187698</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>255</v>
+        <v>18640</v>
       </c>
       <c r="C8" s="1">
-        <v>3057</v>
+        <v>190755</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>419</v>
+        <v>19059</v>
       </c>
       <c r="C9" s="1">
-        <v>5536</v>
+        <v>196291</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>224</v>
+        <v>19283</v>
       </c>
       <c r="C10" s="1">
-        <v>1686</v>
+        <v>197977</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>284</v>
+        <v>19567</v>
       </c>
       <c r="C11" s="1">
-        <v>1698</v>
+        <v>199675</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>144</v>
+        <v>19711</v>
       </c>
       <c r="C12" s="1">
-        <v>1454</v>
+        <v>201129</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>382</v>
+        <v>20094</v>
       </c>
       <c r="C13" s="1">
-        <v>4206</v>
+        <v>205341</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>302</v>
+        <v>20396</v>
       </c>
       <c r="C14" s="1">
-        <v>2885</v>
+        <v>208226</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>355</v>
+        <v>20751</v>
       </c>
       <c r="C15" s="1">
-        <v>3328</v>
+        <v>211554</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>152</v>
+        <v>20903</v>
       </c>
       <c r="C16" s="1">
-        <v>2357</v>
+        <v>213911</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>201</v>
+        <v>21104</v>
       </c>
       <c r="C17" s="1">
-        <v>1883</v>
+        <v>215794</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>214</v>
+        <v>21318</v>
       </c>
       <c r="C18" s="1">
-        <v>1759</v>
+        <v>217553</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>156</v>
+        <v>21474</v>
       </c>
       <c r="C19" s="1">
-        <v>1381</v>
+        <v>218934</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>219</v>
+        <v>21694</v>
       </c>
       <c r="C20" s="1">
-        <v>3142</v>
+        <v>222077</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>635</v>
+        <v>22331</v>
       </c>
       <c r="C21" s="1">
-        <v>11876</v>
+        <v>233960</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>858</v>
+        <v>23189</v>
       </c>
       <c r="C22" s="1">
-        <v>13831</v>
+        <v>247791</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>834</v>
+        <v>24023</v>
       </c>
       <c r="C23" s="1">
-        <v>12161</v>
+        <v>259952</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>1134</v>
+        <v>25158</v>
       </c>
       <c r="C24" s="1">
-        <v>14168</v>
+        <v>274121</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>913</v>
+        <v>26073</v>
       </c>
       <c r="C25" s="1">
-        <v>9866</v>
+        <v>284013</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>936</v>
+        <v>27010</v>
       </c>
       <c r="C26" s="1">
-        <v>15024</v>
+        <v>299042</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>547</v>
+        <v>27557</v>
       </c>
       <c r="C27" s="1">
-        <v>7947</v>
+        <v>306989</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>567</v>
+        <v>28124</v>
       </c>
       <c r="C28" s="1">
-        <v>8449</v>
+        <v>315438</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>532</v>
+        <v>28656</v>
       </c>
       <c r="C29" s="1">
-        <v>5229</v>
+        <v>320667</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>444</v>
+        <v>29101</v>
       </c>
       <c r="C30" s="1">
-        <v>14843</v>
+        <v>335583</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>414</v>
+        <v>29515</v>
       </c>
       <c r="C31" s="1">
-        <v>5629</v>
+        <v>341212</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>605</v>
+        <v>30120</v>
       </c>
       <c r="C32" s="1">
-        <v>8698</v>
+        <v>349910</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>480</v>
+        <v>30602</v>
       </c>
       <c r="C33" s="1">
-        <v>5464</v>
+        <v>355475</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>447</v>
+        <v>31050</v>
       </c>
       <c r="C34" s="1">
-        <v>4618</v>
+        <v>360127</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>372</v>
+        <v>31422</v>
       </c>
       <c r="C35" s="1">
-        <v>5405</v>
+        <v>365532</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,26 +823,13 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>413</v>
+        <v>31835</v>
       </c>
       <c r="C36" s="1">
-        <v>3311</v>
+        <v>368843</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>20200527</v>
-      </c>
-      <c r="B37" s="1">
-        <v>300</v>
-      </c>
-      <c r="C37" s="1">
-        <v>3589</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="13320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="13185"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$36</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$38</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>15585</v>
+        <v>14792</v>
       </c>
       <c r="C3" s="1">
-        <v>151306</v>
+        <v>142447</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>16670</v>
+        <v>15875</v>
       </c>
       <c r="C4" s="1">
-        <v>165745</v>
+        <v>156879</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>17403</v>
+        <v>16608</v>
       </c>
       <c r="C5" s="1">
-        <v>172555</v>
+        <v>163689</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>17922</v>
+        <v>17127</v>
       </c>
       <c r="C6" s="1">
-        <v>182210</v>
+        <v>173344</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>18385</v>
+        <v>17586</v>
       </c>
       <c r="C7" s="1">
-        <v>187698</v>
+        <v>178802</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>18640</v>
+        <v>17841</v>
       </c>
       <c r="C8" s="1">
-        <v>190755</v>
+        <v>181859</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>19059</v>
+        <v>18259</v>
       </c>
       <c r="C9" s="1">
-        <v>196291</v>
+        <v>187393</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>19283</v>
+        <v>18483</v>
       </c>
       <c r="C10" s="1">
-        <v>197977</v>
+        <v>189079</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>19567</v>
+        <v>18767</v>
       </c>
       <c r="C11" s="1">
-        <v>199675</v>
+        <v>190777</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>19711</v>
+        <v>18911</v>
       </c>
       <c r="C12" s="1">
-        <v>201129</v>
+        <v>192231</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>20094</v>
+        <v>19293</v>
       </c>
       <c r="C13" s="1">
-        <v>205341</v>
+        <v>196437</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>20396</v>
+        <v>19595</v>
       </c>
       <c r="C14" s="1">
-        <v>208226</v>
+        <v>199322</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>20751</v>
+        <v>19950</v>
       </c>
       <c r="C15" s="1">
-        <v>211554</v>
+        <v>202650</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>20903</v>
+        <v>20102</v>
       </c>
       <c r="C16" s="1">
-        <v>213911</v>
+        <v>205007</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>21104</v>
+        <v>20303</v>
       </c>
       <c r="C17" s="1">
-        <v>215794</v>
+        <v>206890</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>21318</v>
+        <v>20517</v>
       </c>
       <c r="C18" s="1">
-        <v>217553</v>
+        <v>208649</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>21474</v>
+        <v>20673</v>
       </c>
       <c r="C19" s="1">
-        <v>218934</v>
+        <v>210030</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>21694</v>
+        <v>20892</v>
       </c>
       <c r="C20" s="1">
-        <v>222077</v>
+        <v>213172</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>22331</v>
+        <v>21527</v>
       </c>
       <c r="C21" s="1">
-        <v>233960</v>
+        <v>225048</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>23189</v>
+        <v>22384</v>
       </c>
       <c r="C22" s="1">
-        <v>247791</v>
+        <v>238874</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>24023</v>
+        <v>23218</v>
       </c>
       <c r="C23" s="1">
-        <v>259952</v>
+        <v>251035</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>25158</v>
+        <v>24349</v>
       </c>
       <c r="C24" s="1">
-        <v>274121</v>
+        <v>265189</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>26073</v>
+        <v>25260</v>
       </c>
       <c r="C25" s="1">
-        <v>284013</v>
+        <v>275015</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>27010</v>
+        <v>26196</v>
       </c>
       <c r="C26" s="1">
-        <v>299042</v>
+        <v>290039</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>27557</v>
+        <v>26743</v>
       </c>
       <c r="C27" s="1">
-        <v>306989</v>
+        <v>297986</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>28124</v>
+        <v>27310</v>
       </c>
       <c r="C28" s="1">
-        <v>315438</v>
+        <v>306435</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>28656</v>
+        <v>27842</v>
       </c>
       <c r="C29" s="1">
-        <v>320667</v>
+        <v>311664</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>29101</v>
+        <v>28286</v>
       </c>
       <c r="C30" s="1">
-        <v>335583</v>
+        <v>326507</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>29515</v>
+        <v>28700</v>
       </c>
       <c r="C31" s="1">
-        <v>341212</v>
+        <v>332136</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>30120</v>
+        <v>29305</v>
       </c>
       <c r="C32" s="1">
-        <v>349910</v>
+        <v>340834</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>30602</v>
+        <v>29785</v>
       </c>
       <c r="C33" s="1">
-        <v>355475</v>
+        <v>346298</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>31050</v>
+        <v>30232</v>
       </c>
       <c r="C34" s="1">
-        <v>360127</v>
+        <v>350916</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>31422</v>
+        <v>30604</v>
       </c>
       <c r="C35" s="1">
-        <v>365532</v>
+        <v>356321</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,13 +823,39 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>31835</v>
+        <v>31017</v>
       </c>
       <c r="C36" s="1">
-        <v>368843</v>
+        <v>359632</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>20200527</v>
+      </c>
+      <c r="B37" s="1">
+        <v>31317</v>
+      </c>
+      <c r="C37" s="1">
+        <v>363221</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>20200528</v>
+      </c>
+      <c r="B38" s="1">
+        <v>31945</v>
+      </c>
+      <c r="C38" s="1">
+        <v>369376</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="13185"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25755" windowHeight="13170"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$38</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$39</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>14792</v>
+        <v>14607</v>
       </c>
       <c r="C3" s="1">
-        <v>142447</v>
+        <v>139992</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>15875</v>
+        <v>15691</v>
       </c>
       <c r="C4" s="1">
-        <v>156879</v>
+        <v>154412</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>16608</v>
+        <v>16423</v>
       </c>
       <c r="C5" s="1">
-        <v>163689</v>
+        <v>161219</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>17127</v>
+        <v>16942</v>
       </c>
       <c r="C6" s="1">
-        <v>173344</v>
+        <v>170874</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>17586</v>
+        <v>17401</v>
       </c>
       <c r="C7" s="1">
-        <v>178802</v>
+        <v>176332</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>17841</v>
+        <v>17656</v>
       </c>
       <c r="C8" s="1">
-        <v>181859</v>
+        <v>179389</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>18259</v>
+        <v>18074</v>
       </c>
       <c r="C9" s="1">
-        <v>187393</v>
+        <v>184923</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>18483</v>
+        <v>18298</v>
       </c>
       <c r="C10" s="1">
-        <v>189079</v>
+        <v>186609</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>18767</v>
+        <v>18581</v>
       </c>
       <c r="C11" s="1">
-        <v>190777</v>
+        <v>188303</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>18911</v>
+        <v>18725</v>
       </c>
       <c r="C12" s="1">
-        <v>192231</v>
+        <v>189757</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>19293</v>
+        <v>19107</v>
       </c>
       <c r="C13" s="1">
-        <v>196437</v>
+        <v>193963</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>19595</v>
+        <v>19409</v>
       </c>
       <c r="C14" s="1">
-        <v>199322</v>
+        <v>196848</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>19950</v>
+        <v>19764</v>
       </c>
       <c r="C15" s="1">
-        <v>202650</v>
+        <v>200176</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>20102</v>
+        <v>19916</v>
       </c>
       <c r="C16" s="1">
-        <v>205007</v>
+        <v>202533</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>20303</v>
+        <v>20117</v>
       </c>
       <c r="C17" s="1">
-        <v>206890</v>
+        <v>204416</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>20517</v>
+        <v>20331</v>
       </c>
       <c r="C18" s="1">
-        <v>208649</v>
+        <v>206175</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>20673</v>
+        <v>20487</v>
       </c>
       <c r="C19" s="1">
-        <v>210030</v>
+        <v>207556</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>20892</v>
+        <v>20706</v>
       </c>
       <c r="C20" s="1">
-        <v>213172</v>
+        <v>210698</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>21527</v>
+        <v>21341</v>
       </c>
       <c r="C21" s="1">
-        <v>225048</v>
+        <v>222574</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>22384</v>
+        <v>22197</v>
       </c>
       <c r="C22" s="1">
-        <v>238874</v>
+        <v>236399</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>23218</v>
+        <v>23031</v>
       </c>
       <c r="C23" s="1">
-        <v>251035</v>
+        <v>248560</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>24349</v>
+        <v>24161</v>
       </c>
       <c r="C24" s="1">
-        <v>265189</v>
+        <v>262431</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>25260</v>
+        <v>25072</v>
       </c>
       <c r="C25" s="1">
-        <v>275015</v>
+        <v>272257</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>26196</v>
+        <v>26008</v>
       </c>
       <c r="C26" s="1">
-        <v>290039</v>
+        <v>287281</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>26743</v>
+        <v>26555</v>
       </c>
       <c r="C27" s="1">
-        <v>297986</v>
+        <v>295228</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>27310</v>
+        <v>27122</v>
       </c>
       <c r="C28" s="1">
-        <v>306435</v>
+        <v>303677</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>27842</v>
+        <v>27653</v>
       </c>
       <c r="C29" s="1">
-        <v>311664</v>
+        <v>308905</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>28286</v>
+        <v>28096</v>
       </c>
       <c r="C30" s="1">
-        <v>326507</v>
+        <v>323747</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>28700</v>
+        <v>28510</v>
       </c>
       <c r="C31" s="1">
-        <v>332136</v>
+        <v>329376</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>29305</v>
+        <v>29115</v>
       </c>
       <c r="C32" s="1">
-        <v>340834</v>
+        <v>338074</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>29785</v>
+        <v>29594</v>
       </c>
       <c r="C33" s="1">
-        <v>346298</v>
+        <v>343531</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>30232</v>
+        <v>30041</v>
       </c>
       <c r="C34" s="1">
-        <v>350916</v>
+        <v>348149</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>30604</v>
+        <v>30412</v>
       </c>
       <c r="C35" s="1">
-        <v>356321</v>
+        <v>353550</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,10 +823,10 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>31017</v>
+        <v>30825</v>
       </c>
       <c r="C36" s="1">
-        <v>359632</v>
+        <v>356861</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -836,10 +836,10 @@
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>31317</v>
+        <v>31125</v>
       </c>
       <c r="C37" s="1">
-        <v>363221</v>
+        <v>360450</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -849,13 +849,26 @@
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>31945</v>
+        <v>31753</v>
       </c>
       <c r="C38" s="1">
-        <v>369376</v>
+        <v>366605</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>20200529</v>
+      </c>
+      <c r="B39" s="1">
+        <v>31977</v>
+      </c>
+      <c r="C39" s="1">
+        <v>369580</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$39</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$40</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>14607</v>
+        <v>14396</v>
       </c>
       <c r="C3" s="1">
-        <v>139992</v>
+        <v>137936</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>15691</v>
+        <v>15477</v>
       </c>
       <c r="C4" s="1">
-        <v>154412</v>
+        <v>152343</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>16423</v>
+        <v>16208</v>
       </c>
       <c r="C5" s="1">
-        <v>161219</v>
+        <v>159147</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>16942</v>
+        <v>16727</v>
       </c>
       <c r="C6" s="1">
-        <v>170874</v>
+        <v>168802</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>17401</v>
+        <v>17186</v>
       </c>
       <c r="C7" s="1">
-        <v>176332</v>
+        <v>174260</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>17656</v>
+        <v>17441</v>
       </c>
       <c r="C8" s="1">
-        <v>179389</v>
+        <v>177317</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>18074</v>
+        <v>17859</v>
       </c>
       <c r="C9" s="1">
-        <v>184923</v>
+        <v>182851</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>18298</v>
+        <v>18083</v>
       </c>
       <c r="C10" s="1">
-        <v>186609</v>
+        <v>184537</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>18581</v>
+        <v>18366</v>
       </c>
       <c r="C11" s="1">
-        <v>188303</v>
+        <v>186231</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>18725</v>
+        <v>18510</v>
       </c>
       <c r="C12" s="1">
-        <v>189757</v>
+        <v>187685</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>19107</v>
+        <v>18892</v>
       </c>
       <c r="C13" s="1">
-        <v>193963</v>
+        <v>191891</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>19409</v>
+        <v>19194</v>
       </c>
       <c r="C14" s="1">
-        <v>196848</v>
+        <v>194776</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>19764</v>
+        <v>19548</v>
       </c>
       <c r="C15" s="1">
-        <v>200176</v>
+        <v>198075</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>19916</v>
+        <v>19700</v>
       </c>
       <c r="C16" s="1">
-        <v>202533</v>
+        <v>200432</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>20117</v>
+        <v>19901</v>
       </c>
       <c r="C17" s="1">
-        <v>204416</v>
+        <v>202315</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>20331</v>
+        <v>20115</v>
       </c>
       <c r="C18" s="1">
-        <v>206175</v>
+        <v>204074</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>20487</v>
+        <v>20271</v>
       </c>
       <c r="C19" s="1">
-        <v>207556</v>
+        <v>205455</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>20706</v>
+        <v>20490</v>
       </c>
       <c r="C20" s="1">
-        <v>210698</v>
+        <v>208597</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>21341</v>
+        <v>21125</v>
       </c>
       <c r="C21" s="1">
-        <v>222574</v>
+        <v>220473</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>22197</v>
+        <v>21980</v>
       </c>
       <c r="C22" s="1">
-        <v>236399</v>
+        <v>234296</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>23031</v>
+        <v>22813</v>
       </c>
       <c r="C23" s="1">
-        <v>248560</v>
+        <v>246455</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>24161</v>
+        <v>23942</v>
       </c>
       <c r="C24" s="1">
-        <v>262431</v>
+        <v>260041</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>25072</v>
+        <v>24853</v>
       </c>
       <c r="C25" s="1">
-        <v>272257</v>
+        <v>269867</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>26008</v>
+        <v>25788</v>
       </c>
       <c r="C26" s="1">
-        <v>287281</v>
+        <v>284855</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>26555</v>
+        <v>26335</v>
       </c>
       <c r="C27" s="1">
-        <v>295228</v>
+        <v>292802</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>27122</v>
+        <v>26902</v>
       </c>
       <c r="C28" s="1">
-        <v>303677</v>
+        <v>301251</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>27653</v>
+        <v>27433</v>
       </c>
       <c r="C29" s="1">
-        <v>308905</v>
+        <v>306479</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>28096</v>
+        <v>27871</v>
       </c>
       <c r="C30" s="1">
-        <v>323747</v>
+        <v>321303</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>28510</v>
+        <v>28283</v>
       </c>
       <c r="C31" s="1">
-        <v>329376</v>
+        <v>326905</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>29115</v>
+        <v>28888</v>
       </c>
       <c r="C32" s="1">
-        <v>338074</v>
+        <v>335603</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>29594</v>
+        <v>29367</v>
       </c>
       <c r="C33" s="1">
-        <v>343531</v>
+        <v>341060</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>30041</v>
+        <v>29814</v>
       </c>
       <c r="C34" s="1">
-        <v>348149</v>
+        <v>345678</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>30412</v>
+        <v>30185</v>
       </c>
       <c r="C35" s="1">
-        <v>353550</v>
+        <v>351079</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,10 +823,10 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>30825</v>
+        <v>30598</v>
       </c>
       <c r="C36" s="1">
-        <v>356861</v>
+        <v>354390</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -836,10 +836,10 @@
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>31125</v>
+        <v>30898</v>
       </c>
       <c r="C37" s="1">
-        <v>360450</v>
+        <v>357979</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -849,10 +849,10 @@
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>31753</v>
+        <v>31525</v>
       </c>
       <c r="C38" s="1">
-        <v>366605</v>
+        <v>364113</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -862,13 +862,26 @@
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>31977</v>
+        <v>31748</v>
       </c>
       <c r="C39" s="1">
-        <v>369580</v>
+        <v>367087</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>20200602</v>
+      </c>
+      <c r="B40" s="1">
+        <v>32005</v>
+      </c>
+      <c r="C40" s="1">
+        <v>369949</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25755" windowHeight="13170"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$40</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$41</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>14396</v>
+        <v>14230</v>
       </c>
       <c r="C3" s="1">
-        <v>137936</v>
+        <v>135717</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>15477</v>
+        <v>15310</v>
       </c>
       <c r="C4" s="1">
-        <v>152343</v>
+        <v>150113</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>16208</v>
+        <v>16041</v>
       </c>
       <c r="C5" s="1">
-        <v>159147</v>
+        <v>156917</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>16727</v>
+        <v>16559</v>
       </c>
       <c r="C6" s="1">
-        <v>168802</v>
+        <v>166537</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>17186</v>
+        <v>17018</v>
       </c>
       <c r="C7" s="1">
-        <v>174260</v>
+        <v>171995</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>17441</v>
+        <v>17273</v>
       </c>
       <c r="C8" s="1">
-        <v>177317</v>
+        <v>175052</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>17859</v>
+        <v>17691</v>
       </c>
       <c r="C9" s="1">
-        <v>182851</v>
+        <v>180586</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>18083</v>
+        <v>17915</v>
       </c>
       <c r="C10" s="1">
-        <v>184537</v>
+        <v>182272</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>18366</v>
+        <v>18198</v>
       </c>
       <c r="C11" s="1">
-        <v>186231</v>
+        <v>183966</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>18510</v>
+        <v>18342</v>
       </c>
       <c r="C12" s="1">
-        <v>187685</v>
+        <v>185420</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>18892</v>
+        <v>18724</v>
       </c>
       <c r="C13" s="1">
-        <v>191891</v>
+        <v>189626</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>19194</v>
+        <v>19026</v>
       </c>
       <c r="C14" s="1">
-        <v>194776</v>
+        <v>192511</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>19548</v>
+        <v>19380</v>
       </c>
       <c r="C15" s="1">
-        <v>198075</v>
+        <v>195810</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>19700</v>
+        <v>19532</v>
       </c>
       <c r="C16" s="1">
-        <v>200432</v>
+        <v>198167</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>19901</v>
+        <v>19733</v>
       </c>
       <c r="C17" s="1">
-        <v>202315</v>
+        <v>200050</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>20115</v>
+        <v>19947</v>
       </c>
       <c r="C18" s="1">
-        <v>204074</v>
+        <v>201809</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>20271</v>
+        <v>20103</v>
       </c>
       <c r="C19" s="1">
-        <v>205455</v>
+        <v>203190</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>20490</v>
+        <v>20322</v>
       </c>
       <c r="C20" s="1">
-        <v>208597</v>
+        <v>206332</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>21125</v>
+        <v>20957</v>
       </c>
       <c r="C21" s="1">
-        <v>220473</v>
+        <v>218208</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>21980</v>
+        <v>21810</v>
       </c>
       <c r="C22" s="1">
-        <v>234296</v>
+        <v>231850</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>22813</v>
+        <v>22643</v>
       </c>
       <c r="C23" s="1">
-        <v>246455</v>
+        <v>244009</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>23942</v>
+        <v>23772</v>
       </c>
       <c r="C24" s="1">
-        <v>260041</v>
+        <v>257595</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>24853</v>
+        <v>24682</v>
       </c>
       <c r="C25" s="1">
-        <v>269867</v>
+        <v>267415</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>25788</v>
+        <v>25616</v>
       </c>
       <c r="C26" s="1">
-        <v>284855</v>
+        <v>279885</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>26335</v>
+        <v>26163</v>
       </c>
       <c r="C27" s="1">
-        <v>292802</v>
+        <v>287832</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>26902</v>
+        <v>26730</v>
       </c>
       <c r="C28" s="1">
-        <v>301251</v>
+        <v>296281</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>27433</v>
+        <v>27261</v>
       </c>
       <c r="C29" s="1">
-        <v>306479</v>
+        <v>301509</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>27871</v>
+        <v>27699</v>
       </c>
       <c r="C30" s="1">
-        <v>321303</v>
+        <v>316333</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>28283</v>
+        <v>28111</v>
       </c>
       <c r="C31" s="1">
-        <v>326905</v>
+        <v>321935</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>28888</v>
+        <v>28716</v>
       </c>
       <c r="C32" s="1">
-        <v>335603</v>
+        <v>330633</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>29367</v>
+        <v>29195</v>
       </c>
       <c r="C33" s="1">
-        <v>341060</v>
+        <v>336090</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>29814</v>
+        <v>29641</v>
       </c>
       <c r="C34" s="1">
-        <v>345678</v>
+        <v>340706</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>30185</v>
+        <v>30012</v>
       </c>
       <c r="C35" s="1">
-        <v>351079</v>
+        <v>346107</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,10 +823,10 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>30598</v>
+        <v>30425</v>
       </c>
       <c r="C36" s="1">
-        <v>354390</v>
+        <v>349418</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -836,10 +836,10 @@
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>30898</v>
+        <v>30725</v>
       </c>
       <c r="C37" s="1">
-        <v>357979</v>
+        <v>353007</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -849,10 +849,10 @@
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>31525</v>
+        <v>31350</v>
       </c>
       <c r="C38" s="1">
-        <v>364113</v>
+        <v>359090</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -862,10 +862,10 @@
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>31748</v>
+        <v>31573</v>
       </c>
       <c r="C39" s="1">
-        <v>367087</v>
+        <v>362064</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -875,13 +875,26 @@
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>32005</v>
+        <v>31830</v>
       </c>
       <c r="C40" s="1">
-        <v>369949</v>
+        <v>364926</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>20200603</v>
+      </c>
+      <c r="B41" s="1">
+        <v>32055</v>
+      </c>
+      <c r="C41" s="1">
+        <v>370189</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$41</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$42</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -76,12 +76,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -363,7 +362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -371,7 +370,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,519 +381,452 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>14230</v>
+        <v>14000</v>
       </c>
       <c r="C3" s="1">
-        <v>135717</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>133636</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>15310</v>
+        <v>15080</v>
       </c>
       <c r="C4" s="1">
-        <v>150113</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>148032</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>16041</v>
+        <v>15811</v>
       </c>
       <c r="C5" s="1">
-        <v>156917</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>154836</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>16559</v>
+        <v>16329</v>
       </c>
       <c r="C6" s="1">
-        <v>166537</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>164456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>17018</v>
+        <v>16788</v>
       </c>
       <c r="C7" s="1">
-        <v>171995</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>169914</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>17273</v>
+        <v>17043</v>
       </c>
       <c r="C8" s="1">
-        <v>175052</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>172971</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>17691</v>
+        <v>17461</v>
       </c>
       <c r="C9" s="1">
-        <v>180586</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>178505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>17915</v>
+        <v>17685</v>
       </c>
       <c r="C10" s="1">
-        <v>182272</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>180191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>18198</v>
+        <v>17968</v>
       </c>
       <c r="C11" s="1">
-        <v>183966</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>181885</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>18342</v>
+        <v>18112</v>
       </c>
       <c r="C12" s="1">
-        <v>185420</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>183339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>18724</v>
+        <v>18494</v>
       </c>
       <c r="C13" s="1">
-        <v>189626</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>187545</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>19026</v>
+        <v>18795</v>
       </c>
       <c r="C14" s="1">
-        <v>192511</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>190426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>19380</v>
+        <v>19149</v>
       </c>
       <c r="C15" s="1">
-        <v>195810</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>193725</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>19532</v>
+        <v>19301</v>
       </c>
       <c r="C16" s="1">
-        <v>198167</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>196082</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>19733</v>
+        <v>19501</v>
       </c>
       <c r="C17" s="1">
-        <v>200050</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>197960</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>19947</v>
+        <v>19715</v>
       </c>
       <c r="C18" s="1">
-        <v>201809</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>199719</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>20103</v>
+        <v>19870</v>
       </c>
       <c r="C19" s="1">
-        <v>203190</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>201099</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>20322</v>
+        <v>20088</v>
       </c>
       <c r="C20" s="1">
-        <v>206332</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>204240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>20957</v>
+        <v>20723</v>
       </c>
       <c r="C21" s="1">
-        <v>218208</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>216116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>21810</v>
+        <v>21576</v>
       </c>
       <c r="C22" s="1">
-        <v>231850</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>229758</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>22643</v>
+        <v>22408</v>
       </c>
       <c r="C23" s="1">
-        <v>244009</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>241898</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>23772</v>
+        <v>23536</v>
       </c>
       <c r="C24" s="1">
-        <v>257595</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>255478</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>24682</v>
+        <v>24446</v>
       </c>
       <c r="C25" s="1">
-        <v>267415</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>265298</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>25616</v>
+        <v>25380</v>
       </c>
       <c r="C26" s="1">
-        <v>279885</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>277768</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>26163</v>
+        <v>25927</v>
       </c>
       <c r="C27" s="1">
-        <v>287832</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>285715</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>26730</v>
+        <v>26494</v>
       </c>
       <c r="C28" s="1">
-        <v>296281</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>294164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>27261</v>
+        <v>27025</v>
       </c>
       <c r="C29" s="1">
-        <v>301509</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>299392</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>27699</v>
+        <v>27461</v>
       </c>
       <c r="C30" s="1">
-        <v>316333</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>314214</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>28111</v>
+        <v>27873</v>
       </c>
       <c r="C31" s="1">
-        <v>321935</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>319816</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>28716</v>
+        <v>28478</v>
       </c>
       <c r="C32" s="1">
-        <v>330633</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+        <v>328514</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>29195</v>
+        <v>28957</v>
       </c>
       <c r="C33" s="1">
-        <v>336090</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <v>333971</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>29641</v>
+        <v>29403</v>
       </c>
       <c r="C34" s="1">
-        <v>340706</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>338587</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>30012</v>
+        <v>29774</v>
       </c>
       <c r="C35" s="1">
-        <v>346107</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+        <v>343988</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>30425</v>
+        <v>30187</v>
       </c>
       <c r="C36" s="1">
-        <v>349418</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>347299</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>30725</v>
+        <v>30485</v>
       </c>
       <c r="C37" s="1">
-        <v>353007</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>350806</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>31350</v>
+        <v>31110</v>
       </c>
       <c r="C38" s="1">
-        <v>359090</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>356889</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>31573</v>
+        <v>31333</v>
       </c>
       <c r="C39" s="1">
-        <v>362064</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>359863</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>31830</v>
+        <v>31590</v>
       </c>
       <c r="C40" s="1">
-        <v>364926</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>362725</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>32055</v>
+        <v>31815</v>
       </c>
       <c r="C41" s="1">
-        <v>370189</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
+        <v>367988</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>20200604</v>
+      </c>
+      <c r="B42" s="1">
+        <v>32125</v>
+      </c>
+      <c r="C42" s="1">
+        <v>370627</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$42</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$43</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -76,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -362,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -370,7 +371,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -381,452 +382,545 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>14000</v>
+        <v>13857</v>
       </c>
       <c r="C3" s="1">
-        <v>133636</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>132258</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>15080</v>
+        <v>14935</v>
       </c>
       <c r="C4" s="1">
-        <v>148032</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>146651</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>15811</v>
+        <v>15666</v>
       </c>
       <c r="C5" s="1">
-        <v>154836</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>153455</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>16329</v>
+        <v>16184</v>
       </c>
       <c r="C6" s="1">
-        <v>164456</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>163075</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>16788</v>
+        <v>16643</v>
       </c>
       <c r="C7" s="1">
-        <v>169914</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>168533</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>17043</v>
+        <v>16898</v>
       </c>
       <c r="C8" s="1">
-        <v>172971</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>171590</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>17461</v>
+        <v>17316</v>
       </c>
       <c r="C9" s="1">
-        <v>178505</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>177124</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>17685</v>
+        <v>17540</v>
       </c>
       <c r="C10" s="1">
-        <v>180191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>178810</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>17968</v>
+        <v>17823</v>
       </c>
       <c r="C11" s="1">
-        <v>181885</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>180504</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>18112</v>
+        <v>17967</v>
       </c>
       <c r="C12" s="1">
-        <v>183339</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>181958</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>18494</v>
+        <v>18348</v>
       </c>
       <c r="C13" s="1">
-        <v>187545</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>186157</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>18795</v>
+        <v>18649</v>
       </c>
       <c r="C14" s="1">
-        <v>190426</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>189038</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>19149</v>
+        <v>19002</v>
       </c>
       <c r="C15" s="1">
-        <v>193725</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>192336</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>19301</v>
+        <v>19154</v>
       </c>
       <c r="C16" s="1">
-        <v>196082</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>194693</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>19501</v>
+        <v>19354</v>
       </c>
       <c r="C17" s="1">
-        <v>197960</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>196571</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>19715</v>
+        <v>19568</v>
       </c>
       <c r="C18" s="1">
-        <v>199719</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>198330</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>19870</v>
+        <v>19723</v>
       </c>
       <c r="C19" s="1">
-        <v>201099</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>199710</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>20088</v>
+        <v>19941</v>
       </c>
       <c r="C20" s="1">
-        <v>204240</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>202851</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>20723</v>
+        <v>20576</v>
       </c>
       <c r="C21" s="1">
-        <v>216116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>214727</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>21576</v>
+        <v>21427</v>
       </c>
       <c r="C22" s="1">
-        <v>229758</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>228251</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>22408</v>
+        <v>22259</v>
       </c>
       <c r="C23" s="1">
-        <v>241898</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>240391</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>23536</v>
+        <v>23387</v>
       </c>
       <c r="C24" s="1">
-        <v>255478</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>253971</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>24446</v>
+        <v>24297</v>
       </c>
       <c r="C25" s="1">
-        <v>265298</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>263791</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>25380</v>
+        <v>25230</v>
       </c>
       <c r="C26" s="1">
-        <v>277768</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>276195</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>25927</v>
+        <v>25775</v>
       </c>
       <c r="C27" s="1">
-        <v>285715</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>284093</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>26494</v>
+        <v>26342</v>
       </c>
       <c r="C28" s="1">
-        <v>294164</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>292542</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>27025</v>
+        <v>26872</v>
       </c>
       <c r="C29" s="1">
-        <v>299392</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>297767</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>27461</v>
+        <v>27308</v>
       </c>
       <c r="C30" s="1">
-        <v>314214</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>312589</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>27873</v>
+        <v>27720</v>
       </c>
       <c r="C31" s="1">
-        <v>319816</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>318191</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>28478</v>
+        <v>28325</v>
       </c>
       <c r="C32" s="1">
-        <v>328514</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>326889</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>28957</v>
+        <v>28804</v>
       </c>
       <c r="C33" s="1">
-        <v>333971</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>332346</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>29403</v>
+        <v>29249</v>
       </c>
       <c r="C34" s="1">
-        <v>338587</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>336957</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>29774</v>
+        <v>29620</v>
       </c>
       <c r="C35" s="1">
-        <v>343988</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>342358</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>30187</v>
+        <v>30032</v>
       </c>
       <c r="C36" s="1">
-        <v>347299</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>345668</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>30485</v>
+        <v>30330</v>
       </c>
       <c r="C37" s="1">
-        <v>350806</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>349175</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>31110</v>
+        <v>30954</v>
       </c>
       <c r="C38" s="1">
-        <v>356889</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>355246</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>31333</v>
+        <v>31177</v>
       </c>
       <c r="C39" s="1">
-        <v>359863</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>358220</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>31590</v>
+        <v>31434</v>
       </c>
       <c r="C40" s="1">
-        <v>362725</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+        <v>361082</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>31815</v>
+        <v>31658</v>
       </c>
       <c r="C41" s="1">
-        <v>367988</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+        <v>366332</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>32125</v>
+        <v>31968</v>
       </c>
       <c r="C42" s="1">
-        <v>370627</v>
-      </c>
+        <v>368971</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>20200605</v>
+      </c>
+      <c r="B43" s="1">
+        <v>32170</v>
+      </c>
+      <c r="C43" s="1">
+        <v>371114</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$43</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$44</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -76,12 +76,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -363,7 +362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -371,7 +370,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,545 +381,474 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>13857</v>
+        <v>13733</v>
       </c>
       <c r="C3" s="1">
-        <v>132258</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>131125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>14935</v>
+        <v>14809</v>
       </c>
       <c r="C4" s="1">
-        <v>146651</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>145515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>15666</v>
+        <v>15537</v>
       </c>
       <c r="C5" s="1">
-        <v>153455</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>152087</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>16184</v>
+        <v>16055</v>
       </c>
       <c r="C6" s="1">
-        <v>163075</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>161707</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>16643</v>
+        <v>16514</v>
       </c>
       <c r="C7" s="1">
-        <v>168533</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>167165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>16898</v>
+        <v>16769</v>
       </c>
       <c r="C8" s="1">
-        <v>171590</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>170222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>17316</v>
+        <v>17186</v>
       </c>
       <c r="C9" s="1">
-        <v>177124</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>175742</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>17540</v>
+        <v>17410</v>
       </c>
       <c r="C10" s="1">
-        <v>178810</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>177428</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>17823</v>
+        <v>17693</v>
       </c>
       <c r="C11" s="1">
-        <v>180504</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>179122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>17967</v>
+        <v>17837</v>
       </c>
       <c r="C12" s="1">
-        <v>181958</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>180576</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>18348</v>
+        <v>18217</v>
       </c>
       <c r="C13" s="1">
-        <v>186157</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>184766</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>18649</v>
+        <v>18517</v>
       </c>
       <c r="C14" s="1">
-        <v>189038</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>187645</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>19002</v>
+        <v>18869</v>
       </c>
       <c r="C15" s="1">
-        <v>192336</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>190941</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>19154</v>
+        <v>19021</v>
       </c>
       <c r="C16" s="1">
-        <v>194693</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>193298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>19354</v>
+        <v>19221</v>
       </c>
       <c r="C17" s="1">
-        <v>196571</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>195176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>19568</v>
+        <v>19435</v>
       </c>
       <c r="C18" s="1">
-        <v>198330</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>196935</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>19723</v>
+        <v>19590</v>
       </c>
       <c r="C19" s="1">
-        <v>199710</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>198315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>19941</v>
+        <v>19807</v>
       </c>
       <c r="C20" s="1">
-        <v>202851</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>201455</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>20576</v>
+        <v>20442</v>
       </c>
       <c r="C21" s="1">
-        <v>214727</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>213331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>21427</v>
+        <v>21293</v>
       </c>
       <c r="C22" s="1">
-        <v>228251</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>226855</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>22259</v>
+        <v>22125</v>
       </c>
       <c r="C23" s="1">
-        <v>240391</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>238995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>23387</v>
+        <v>23253</v>
       </c>
       <c r="C24" s="1">
-        <v>253971</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>252575</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>24297</v>
+        <v>24163</v>
       </c>
       <c r="C25" s="1">
-        <v>263791</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>262395</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>25230</v>
+        <v>25096</v>
       </c>
       <c r="C26" s="1">
-        <v>276195</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>274799</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>25775</v>
+        <v>25640</v>
       </c>
       <c r="C27" s="1">
-        <v>284093</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>282696</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>26342</v>
+        <v>26207</v>
       </c>
       <c r="C28" s="1">
-        <v>292542</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>291145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>26872</v>
+        <v>26736</v>
       </c>
       <c r="C29" s="1">
-        <v>297767</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>296360</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>27308</v>
+        <v>27171</v>
       </c>
       <c r="C30" s="1">
-        <v>312589</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>311181</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>27720</v>
+        <v>27583</v>
       </c>
       <c r="C31" s="1">
-        <v>318191</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>316783</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>28325</v>
+        <v>28187</v>
       </c>
       <c r="C32" s="1">
-        <v>326889</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+        <v>325480</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>28804</v>
+        <v>28666</v>
       </c>
       <c r="C33" s="1">
-        <v>332346</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <v>330937</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>29249</v>
+        <v>29110</v>
       </c>
       <c r="C34" s="1">
-        <v>336957</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>335545</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>29620</v>
+        <v>29479</v>
       </c>
       <c r="C35" s="1">
-        <v>342358</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+        <v>340942</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>30032</v>
+        <v>29888</v>
       </c>
       <c r="C36" s="1">
-        <v>345668</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>344244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>30330</v>
+        <v>30186</v>
       </c>
       <c r="C37" s="1">
-        <v>349175</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>347751</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>30954</v>
+        <v>30810</v>
       </c>
       <c r="C38" s="1">
-        <v>355246</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>353822</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>31177</v>
+        <v>31033</v>
       </c>
       <c r="C39" s="1">
-        <v>358220</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>356796</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>31434</v>
+        <v>31290</v>
       </c>
       <c r="C40" s="1">
-        <v>361082</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>359658</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>31658</v>
+        <v>31514</v>
       </c>
       <c r="C41" s="1">
-        <v>366332</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+        <v>364908</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>31968</v>
+        <v>31824</v>
       </c>
       <c r="C42" s="1">
-        <v>368971</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+        <v>367547</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>32170</v>
+        <v>32025</v>
       </c>
       <c r="C43" s="1">
-        <v>371114</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+        <v>369689</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>20200608</v>
+      </c>
+      <c r="B44" s="1">
+        <v>32216</v>
+      </c>
+      <c r="C44" s="1">
+        <v>371909</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -15,7 +15,7 @@
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$44</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$45</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -76,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -362,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -370,7 +371,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -381,474 +382,571 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>13733</v>
+        <v>13567</v>
       </c>
       <c r="C3" s="1">
-        <v>131125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>129748</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>14809</v>
+        <v>14640</v>
       </c>
       <c r="C4" s="1">
-        <v>145515</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>144114</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>15537</v>
+        <v>15368</v>
       </c>
       <c r="C5" s="1">
-        <v>152087</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>150686</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>16055</v>
+        <v>15885</v>
       </c>
       <c r="C6" s="1">
-        <v>161707</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>160303</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>16514</v>
+        <v>16344</v>
       </c>
       <c r="C7" s="1">
-        <v>167165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>165761</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>16769</v>
+        <v>16597</v>
       </c>
       <c r="C8" s="1">
-        <v>170222</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>168778</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>17186</v>
+        <v>17014</v>
       </c>
       <c r="C9" s="1">
-        <v>175742</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>174298</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>17410</v>
+        <v>17238</v>
       </c>
       <c r="C10" s="1">
-        <v>177428</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>175984</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>17693</v>
+        <v>17521</v>
       </c>
       <c r="C11" s="1">
-        <v>179122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>177678</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>17837</v>
+        <v>17665</v>
       </c>
       <c r="C12" s="1">
-        <v>180576</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>179132</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>18217</v>
+        <v>18045</v>
       </c>
       <c r="C13" s="1">
-        <v>184766</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>183322</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>18517</v>
+        <v>18345</v>
       </c>
       <c r="C14" s="1">
-        <v>187645</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>186201</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>18869</v>
+        <v>18697</v>
       </c>
       <c r="C15" s="1">
-        <v>190941</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>189497</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>19021</v>
+        <v>18849</v>
       </c>
       <c r="C16" s="1">
-        <v>193298</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>191854</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>19221</v>
+        <v>19048</v>
       </c>
       <c r="C17" s="1">
-        <v>195176</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>193726</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>19435</v>
+        <v>19262</v>
       </c>
       <c r="C18" s="1">
-        <v>196935</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>195485</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>19590</v>
+        <v>19417</v>
       </c>
       <c r="C19" s="1">
-        <v>198315</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>196865</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>19807</v>
+        <v>19634</v>
       </c>
       <c r="C20" s="1">
-        <v>201455</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>200005</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>20442</v>
+        <v>20269</v>
       </c>
       <c r="C21" s="1">
-        <v>213331</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>211881</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>21293</v>
+        <v>21120</v>
       </c>
       <c r="C22" s="1">
-        <v>226855</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>225405</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>22125</v>
+        <v>21952</v>
       </c>
       <c r="C23" s="1">
-        <v>238995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>237545</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>23253</v>
+        <v>23079</v>
       </c>
       <c r="C24" s="1">
-        <v>252575</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>251074</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>24163</v>
+        <v>23989</v>
       </c>
       <c r="C25" s="1">
-        <v>262395</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>260894</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>25096</v>
+        <v>24922</v>
       </c>
       <c r="C26" s="1">
-        <v>274799</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>273298</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>25640</v>
+        <v>25466</v>
       </c>
       <c r="C27" s="1">
-        <v>282696</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>281195</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>26207</v>
+        <v>26033</v>
       </c>
       <c r="C28" s="1">
-        <v>291145</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>289644</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>26736</v>
+        <v>26561</v>
       </c>
       <c r="C29" s="1">
-        <v>296360</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>294856</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>27171</v>
+        <v>26996</v>
       </c>
       <c r="C30" s="1">
-        <v>311181</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>309677</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>27583</v>
+        <v>27408</v>
       </c>
       <c r="C31" s="1">
-        <v>316783</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>315279</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>28187</v>
+        <v>28010</v>
       </c>
       <c r="C32" s="1">
-        <v>325480</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>323858</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>28666</v>
+        <v>28489</v>
       </c>
       <c r="C33" s="1">
-        <v>330937</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>329315</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>29110</v>
+        <v>28933</v>
       </c>
       <c r="C34" s="1">
-        <v>335545</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>333923</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>29479</v>
+        <v>29301</v>
       </c>
       <c r="C35" s="1">
-        <v>340942</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>339318</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>29888</v>
+        <v>29710</v>
       </c>
       <c r="C36" s="1">
-        <v>344244</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>342620</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>30186</v>
+        <v>30008</v>
       </c>
       <c r="C37" s="1">
-        <v>347751</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>346127</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>30810</v>
+        <v>30631</v>
       </c>
       <c r="C38" s="1">
-        <v>353822</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>352177</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>31033</v>
+        <v>30853</v>
       </c>
       <c r="C39" s="1">
-        <v>356796</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>355140</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>31290</v>
+        <v>31110</v>
       </c>
       <c r="C40" s="1">
-        <v>359658</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+        <v>358002</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>31514</v>
+        <v>31334</v>
       </c>
       <c r="C41" s="1">
-        <v>364908</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+        <v>363252</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>31824</v>
+        <v>31643</v>
       </c>
       <c r="C42" s="1">
-        <v>367547</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+        <v>365888</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>32025</v>
+        <v>31844</v>
       </c>
       <c r="C43" s="1">
-        <v>369689</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+        <v>368030</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>20200608</v>
       </c>
       <c r="B44" s="1">
-        <v>32216</v>
+        <v>32035</v>
       </c>
       <c r="C44" s="1">
-        <v>371909</v>
-      </c>
+        <v>370250</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>20200609</v>
+      </c>
+      <c r="B45" s="1">
+        <v>32255</v>
+      </c>
+      <c r="C45" s="1">
+        <v>372034</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="13320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$33</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$46</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -41,7 +41,7 @@
     <t>Kurzarbeit/Schlechtwetter - Tag Entscheid</t>
   </si>
   <si>
-    <t>20200301 - 20200405</t>
+    <t>2020031 - 20200405</t>
   </si>
 </sst>
 </file>
@@ -76,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -362,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -370,7 +371,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -381,353 +382,584 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>16655</v>
+        <v>13377</v>
       </c>
       <c r="C3" s="1">
-        <v>164332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>128128</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>17733</v>
+        <v>14449</v>
       </c>
       <c r="C4" s="1">
-        <v>178788</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>142469</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>18467</v>
+        <v>15177</v>
       </c>
       <c r="C5" s="1">
-        <v>185618</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>149041</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>18987</v>
+        <v>15694</v>
       </c>
       <c r="C6" s="1">
-        <v>195280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>158658</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>19450</v>
+        <v>16153</v>
       </c>
       <c r="C7" s="1">
-        <v>200768</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>164116</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
-      <c r="B8" s="1">
-        <v>19705</v>
+      <c r="B8" s="3">
+        <v>16406</v>
       </c>
       <c r="C8" s="1">
-        <v>203825</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>167133</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="1">
-        <v>20125</v>
+        <v>16823</v>
       </c>
       <c r="C9" s="1">
-        <v>209368</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>172653</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>20350</v>
+        <v>17047</v>
       </c>
       <c r="C10" s="1">
-        <v>211056</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>174339</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>20635</v>
+        <v>17330</v>
       </c>
       <c r="C11" s="1">
-        <v>212760</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>176033</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>20779</v>
+        <v>17474</v>
       </c>
       <c r="C12" s="1">
-        <v>214214</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>177487</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>21163</v>
+        <v>17853</v>
       </c>
       <c r="C13" s="1">
-        <v>218432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>181618</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>21468</v>
+        <v>18153</v>
       </c>
       <c r="C14" s="1">
-        <v>221327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>184497</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>21826</v>
+        <v>18505</v>
       </c>
       <c r="C15" s="1">
-        <v>224669</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>187793</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>21978</v>
+        <v>18657</v>
       </c>
       <c r="C16" s="1">
-        <v>227026</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>190150</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>22181</v>
+        <v>18856</v>
       </c>
       <c r="C17" s="1">
-        <v>228927</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>192022</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>22398</v>
+        <v>19070</v>
       </c>
       <c r="C18" s="1">
-        <v>230689</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>193781</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>22555</v>
+        <v>19225</v>
       </c>
       <c r="C19" s="1">
-        <v>232090</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>195161</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>22775</v>
+        <v>19442</v>
       </c>
       <c r="C20" s="1">
-        <v>235233</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>198301</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>23413</v>
+        <v>20077</v>
       </c>
       <c r="C21" s="1">
-        <v>247119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>210177</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>24272</v>
+        <v>20927</v>
       </c>
       <c r="C22" s="1">
-        <v>260951</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>223699</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>25107</v>
+        <v>21759</v>
       </c>
       <c r="C23" s="1">
-        <v>273115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>235839</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>26245</v>
+        <v>22886</v>
       </c>
       <c r="C24" s="1">
-        <v>287316</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>249368</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>27161</v>
+        <v>23796</v>
       </c>
       <c r="C25" s="1">
-        <v>297209</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>259188</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>28099</v>
+        <v>24727</v>
       </c>
       <c r="C26" s="1">
-        <v>312244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>271581</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
-      <c r="B27" s="1">
-        <v>28646</v>
+      <c r="B27" s="3">
+        <v>25271</v>
       </c>
       <c r="C27" s="1">
-        <v>320191</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>279478</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="1">
-        <v>29214</v>
+        <v>25838</v>
       </c>
       <c r="C28" s="1">
-        <v>328642</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>287927</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>29749</v>
+        <v>26366</v>
       </c>
       <c r="C29" s="1">
-        <v>333878</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>293139</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>30194</v>
+        <v>26800</v>
       </c>
       <c r="C30" s="1">
-        <v>348794</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>307953</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>30612</v>
+        <v>27212</v>
       </c>
       <c r="C31" s="1">
-        <v>354440</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>313555</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>31219</v>
+        <v>27813</v>
       </c>
       <c r="C32" s="1">
-        <v>363158</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>322133</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>31702</v>
+        <v>28292</v>
       </c>
       <c r="C33" s="1">
-        <v>368726</v>
-      </c>
+        <v>327590</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>20200522</v>
+      </c>
+      <c r="B34" s="1">
+        <v>28736</v>
+      </c>
+      <c r="C34" s="1">
+        <v>332198</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>20200525</v>
+      </c>
+      <c r="B35" s="1">
+        <v>29104</v>
+      </c>
+      <c r="C35" s="1">
+        <v>337593</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>20200526</v>
+      </c>
+      <c r="B36" s="1">
+        <v>29512</v>
+      </c>
+      <c r="C36" s="1">
+        <v>340892</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>20200527</v>
+      </c>
+      <c r="B37" s="1">
+        <v>29810</v>
+      </c>
+      <c r="C37" s="1">
+        <v>344399</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>20200528</v>
+      </c>
+      <c r="B38" s="1">
+        <v>30433</v>
+      </c>
+      <c r="C38" s="1">
+        <v>350449</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>20200529</v>
+      </c>
+      <c r="B39" s="1">
+        <v>30655</v>
+      </c>
+      <c r="C39" s="1">
+        <v>353412</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>20200602</v>
+      </c>
+      <c r="B40" s="1">
+        <v>30912</v>
+      </c>
+      <c r="C40" s="1">
+        <v>356274</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>20200603</v>
+      </c>
+      <c r="B41" s="1">
+        <v>31136</v>
+      </c>
+      <c r="C41" s="1">
+        <v>361524</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>20200604</v>
+      </c>
+      <c r="B42" s="1">
+        <v>31445</v>
+      </c>
+      <c r="C42" s="1">
+        <v>364160</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>20200605</v>
+      </c>
+      <c r="B43" s="1">
+        <v>31646</v>
+      </c>
+      <c r="C43" s="1">
+        <v>366302</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>20200608</v>
+      </c>
+      <c r="B44" s="1">
+        <v>31837</v>
+      </c>
+      <c r="C44" s="1">
+        <v>368522</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>20200609</v>
+      </c>
+      <c r="B45" s="1">
+        <v>32057</v>
+      </c>
+      <c r="C45" s="1">
+        <v>370306</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>20200610</v>
+      </c>
+      <c r="B46" s="1">
+        <v>32296</v>
+      </c>
+      <c r="C46" s="1">
+        <v>372263</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$46</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$47</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -41,7 +41,7 @@
     <t>Kurzarbeit/Schlechtwetter - Tag Entscheid</t>
   </si>
   <si>
-    <t>2020031 - 20200405</t>
+    <t>20200301 - 20200405</t>
   </si>
 </sst>
 </file>
@@ -76,12 +76,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -363,7 +362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -371,7 +370,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,584 +381,507 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>13377</v>
+        <v>13171</v>
       </c>
       <c r="C3" s="1">
-        <v>128128</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>125524</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>14449</v>
+        <v>14241</v>
       </c>
       <c r="C4" s="1">
-        <v>142469</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>139852</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>15177</v>
+        <v>14969</v>
       </c>
       <c r="C5" s="1">
-        <v>149041</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>146424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>15694</v>
+        <v>15486</v>
       </c>
       <c r="C6" s="1">
-        <v>158658</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>156041</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>16153</v>
+        <v>15945</v>
       </c>
       <c r="C7" s="1">
-        <v>164116</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>161499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>16406</v>
+        <v>16198</v>
       </c>
       <c r="C8" s="1">
-        <v>167133</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>164516</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
-      <c r="B9" s="1">
-        <v>16823</v>
+      <c r="B9" s="3">
+        <v>16615</v>
       </c>
       <c r="C9" s="1">
-        <v>172653</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>170036</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
       <c r="B10" s="1">
-        <v>17047</v>
+        <v>16839</v>
       </c>
       <c r="C10" s="1">
-        <v>174339</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>171722</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
       <c r="B11" s="1">
-        <v>17330</v>
+        <v>17122</v>
       </c>
       <c r="C11" s="1">
-        <v>176033</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>173416</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>17474</v>
+        <v>17266</v>
       </c>
       <c r="C12" s="1">
-        <v>177487</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>174870</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>17853</v>
+        <v>17645</v>
       </c>
       <c r="C13" s="1">
-        <v>181618</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>179001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>18153</v>
+        <v>17945</v>
       </c>
       <c r="C14" s="1">
-        <v>184497</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>181880</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>18505</v>
+        <v>18297</v>
       </c>
       <c r="C15" s="1">
-        <v>187793</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>185176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>18657</v>
+        <v>18448</v>
       </c>
       <c r="C16" s="1">
-        <v>190150</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+        <v>187499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>18856</v>
+        <v>18647</v>
       </c>
       <c r="C17" s="1">
-        <v>192022</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+        <v>189371</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>19070</v>
+        <v>18860</v>
       </c>
       <c r="C18" s="1">
-        <v>193781</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+        <v>191129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>19225</v>
+        <v>19015</v>
       </c>
       <c r="C19" s="1">
-        <v>195161</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+        <v>192509</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>19442</v>
+        <v>19231</v>
       </c>
       <c r="C20" s="1">
-        <v>198301</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+        <v>195648</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>20077</v>
+        <v>19866</v>
       </c>
       <c r="C21" s="1">
-        <v>210177</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+        <v>207524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>20927</v>
+        <v>20715</v>
       </c>
       <c r="C22" s="1">
-        <v>223699</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+        <v>221045</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>21759</v>
+        <v>21547</v>
       </c>
       <c r="C23" s="1">
-        <v>235839</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+        <v>233185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>22886</v>
+        <v>22673</v>
       </c>
       <c r="C24" s="1">
-        <v>249368</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+        <v>246713</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>23796</v>
+        <v>23583</v>
       </c>
       <c r="C25" s="1">
-        <v>259188</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+        <v>256533</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>24727</v>
+        <v>24513</v>
       </c>
       <c r="C26" s="1">
-        <v>271581</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>268919</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>25271</v>
+        <v>25057</v>
       </c>
       <c r="C27" s="1">
-        <v>279478</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>276816</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
-      <c r="B28" s="1">
-        <v>25838</v>
+      <c r="B28" s="3">
+        <v>25624</v>
       </c>
       <c r="C28" s="1">
-        <v>287927</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>285265</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
       <c r="B29" s="1">
-        <v>26366</v>
+        <v>26152</v>
       </c>
       <c r="C29" s="1">
-        <v>293139</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>290477</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
       <c r="B30" s="1">
-        <v>26800</v>
+        <v>26586</v>
       </c>
       <c r="C30" s="1">
-        <v>307953</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>305291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>27212</v>
+        <v>26998</v>
       </c>
       <c r="C31" s="1">
-        <v>313555</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>310893</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>27813</v>
+        <v>27599</v>
       </c>
       <c r="C32" s="1">
-        <v>322133</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+        <v>319471</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>28292</v>
+        <v>28078</v>
       </c>
       <c r="C33" s="1">
-        <v>327590</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+        <v>324928</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>28736</v>
+        <v>28522</v>
       </c>
       <c r="C34" s="1">
-        <v>332198</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+        <v>329536</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>29104</v>
+        <v>28890</v>
       </c>
       <c r="C35" s="1">
-        <v>337593</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+        <v>334931</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>29512</v>
+        <v>29298</v>
       </c>
       <c r="C36" s="1">
-        <v>340892</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+        <v>338230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>29810</v>
+        <v>29596</v>
       </c>
       <c r="C37" s="1">
-        <v>344399</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+        <v>341737</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>30433</v>
+        <v>30219</v>
       </c>
       <c r="C38" s="1">
-        <v>350449</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>347787</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>30655</v>
+        <v>30441</v>
       </c>
       <c r="C39" s="1">
-        <v>353412</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+        <v>350750</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>30912</v>
+        <v>30698</v>
       </c>
       <c r="C40" s="1">
-        <v>356274</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+        <v>353612</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>31136</v>
+        <v>30922</v>
       </c>
       <c r="C41" s="1">
-        <v>361524</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+        <v>358862</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>31445</v>
+        <v>31231</v>
       </c>
       <c r="C42" s="1">
-        <v>364160</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+        <v>361498</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>31646</v>
+        <v>31432</v>
       </c>
       <c r="C43" s="1">
-        <v>366302</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+        <v>363640</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>20200608</v>
       </c>
       <c r="B44" s="1">
-        <v>31837</v>
+        <v>31623</v>
       </c>
       <c r="C44" s="1">
-        <v>368522</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+        <v>365860</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>20200609</v>
       </c>
       <c r="B45" s="1">
-        <v>32057</v>
+        <v>31842</v>
       </c>
       <c r="C45" s="1">
-        <v>370306</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+        <v>367565</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>20200610</v>
       </c>
       <c r="B46" s="1">
-        <v>32296</v>
+        <v>32080</v>
       </c>
       <c r="C46" s="1">
-        <v>372263</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
+        <v>369519</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>20200611</v>
+      </c>
+      <c r="B47" s="1">
+        <v>32333</v>
+      </c>
+      <c r="C47" s="1">
+        <v>372430</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11850"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26040" windowHeight="11625"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$47</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$48</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -76,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -362,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -370,7 +371,7 @@
     <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -381,507 +382,615 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>13171</v>
+        <v>12594</v>
       </c>
       <c r="C3" s="1">
-        <v>125524</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>120906</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>14241</v>
+        <v>13660</v>
       </c>
       <c r="C4" s="1">
-        <v>139852</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>135225</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>14969</v>
+        <v>14388</v>
       </c>
       <c r="C5" s="1">
-        <v>146424</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>141797</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>15486</v>
+        <v>14905</v>
       </c>
       <c r="C6" s="1">
-        <v>156041</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>151414</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>15945</v>
+        <v>15364</v>
       </c>
       <c r="C7" s="1">
-        <v>161499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>156872</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>16198</v>
+        <v>15617</v>
       </c>
       <c r="C8" s="1">
-        <v>164516</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>159889</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>20200415</v>
       </c>
       <c r="B9" s="3">
-        <v>16615</v>
+        <v>16034</v>
       </c>
       <c r="C9" s="1">
-        <v>170036</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>165409</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>20200416</v>
       </c>
-      <c r="B10" s="1">
-        <v>16839</v>
+      <c r="B10" s="3">
+        <v>16257</v>
       </c>
       <c r="C10" s="1">
-        <v>171722</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+        <v>167056</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>20200417</v>
       </c>
-      <c r="B11" s="1">
-        <v>17122</v>
+      <c r="B11" s="3">
+        <v>16540</v>
       </c>
       <c r="C11" s="1">
-        <v>173416</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+        <v>168750</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
       <c r="B12" s="1">
-        <v>17266</v>
+        <v>16683</v>
       </c>
       <c r="C12" s="1">
-        <v>174870</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+        <v>170201</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
       <c r="B13" s="1">
-        <v>17645</v>
+        <v>17062</v>
       </c>
       <c r="C13" s="1">
-        <v>179001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+        <v>174332</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>17945</v>
+        <v>17362</v>
       </c>
       <c r="C14" s="1">
-        <v>181880</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+        <v>177211</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>18297</v>
+        <v>17714</v>
       </c>
       <c r="C15" s="1">
-        <v>185176</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+        <v>180507</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>18448</v>
+        <v>17865</v>
       </c>
       <c r="C16" s="1">
-        <v>187499</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>182830</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>18647</v>
+        <v>18064</v>
       </c>
       <c r="C17" s="1">
-        <v>189371</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>184702</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>18860</v>
+        <v>18277</v>
       </c>
       <c r="C18" s="1">
-        <v>191129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>186460</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>19015</v>
+        <v>18432</v>
       </c>
       <c r="C19" s="1">
-        <v>192509</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>187840</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>19231</v>
+        <v>18648</v>
       </c>
       <c r="C20" s="1">
-        <v>195648</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>190979</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>19866</v>
+        <v>19283</v>
       </c>
       <c r="C21" s="1">
-        <v>207524</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+        <v>202855</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>20715</v>
+        <v>20131</v>
       </c>
       <c r="C22" s="1">
-        <v>221045</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+        <v>216375</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>21547</v>
+        <v>20963</v>
       </c>
       <c r="C23" s="1">
-        <v>233185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+        <v>228515</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>22673</v>
+        <v>22088</v>
       </c>
       <c r="C24" s="1">
-        <v>246713</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+        <v>242037</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
-      <c r="B25" s="3">
-        <v>23583</v>
+      <c r="B25" s="1">
+        <v>22998</v>
       </c>
       <c r="C25" s="1">
-        <v>256533</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+        <v>251857</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>24513</v>
+        <v>23928</v>
       </c>
       <c r="C26" s="1">
-        <v>268919</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+        <v>264243</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
       <c r="B27" s="3">
-        <v>25057</v>
+        <v>24472</v>
       </c>
       <c r="C27" s="1">
-        <v>276816</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+        <v>272140</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
       <c r="B28" s="3">
-        <v>25624</v>
+        <v>25039</v>
       </c>
       <c r="C28" s="1">
-        <v>285265</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>280589</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>20200514</v>
       </c>
-      <c r="B29" s="1">
-        <v>26152</v>
+      <c r="B29" s="3">
+        <v>25567</v>
       </c>
       <c r="C29" s="1">
-        <v>290477</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>285801</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>20200515</v>
       </c>
-      <c r="B30" s="1">
-        <v>26586</v>
+      <c r="B30" s="3">
+        <v>26001</v>
       </c>
       <c r="C30" s="1">
-        <v>305291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>300615</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
       <c r="B31" s="1">
-        <v>26998</v>
+        <v>26413</v>
       </c>
       <c r="C31" s="1">
-        <v>310893</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>306217</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
       <c r="B32" s="1">
-        <v>27599</v>
+        <v>27014</v>
       </c>
       <c r="C32" s="1">
-        <v>319471</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>314795</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>28078</v>
+        <v>27493</v>
       </c>
       <c r="C33" s="1">
-        <v>324928</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>320252</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>28522</v>
+        <v>27937</v>
       </c>
       <c r="C34" s="1">
-        <v>329536</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>324860</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>28890</v>
+        <v>28305</v>
       </c>
       <c r="C35" s="1">
-        <v>334931</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>330255</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>29298</v>
+        <v>28713</v>
       </c>
       <c r="C36" s="1">
-        <v>338230</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>333554</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>29596</v>
+        <v>29010</v>
       </c>
       <c r="C37" s="1">
-        <v>341737</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>337053</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>30219</v>
+        <v>29633</v>
       </c>
       <c r="C38" s="1">
-        <v>347787</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>343103</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>30441</v>
+        <v>29855</v>
       </c>
       <c r="C39" s="1">
-        <v>350750</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>346066</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>30698</v>
+        <v>30112</v>
       </c>
       <c r="C40" s="1">
-        <v>353612</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+        <v>348928</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>30922</v>
+        <v>30336</v>
       </c>
       <c r="C41" s="1">
-        <v>358862</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+        <v>354178</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>31231</v>
+        <v>30645</v>
       </c>
       <c r="C42" s="1">
-        <v>361498</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+        <v>356814</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>31432</v>
+        <v>30846</v>
       </c>
       <c r="C43" s="1">
-        <v>363640</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+        <v>358956</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>20200608</v>
       </c>
       <c r="B44" s="1">
-        <v>31623</v>
+        <v>31037</v>
       </c>
       <c r="C44" s="1">
-        <v>365860</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+        <v>361176</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>20200609</v>
       </c>
       <c r="B45" s="1">
-        <v>31842</v>
+        <v>31256</v>
       </c>
       <c r="C45" s="1">
-        <v>367565</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+        <v>362881</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>20200610</v>
       </c>
       <c r="B46" s="1">
-        <v>32080</v>
+        <v>31494</v>
       </c>
       <c r="C46" s="1">
-        <v>369519</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+        <v>364835</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>20200611</v>
       </c>
       <c r="B47" s="1">
-        <v>32333</v>
+        <v>31747</v>
       </c>
       <c r="C47" s="1">
-        <v>372430</v>
-      </c>
+        <v>367746</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>20200612</v>
+      </c>
+      <c r="B48" s="1">
+        <v>32344</v>
+      </c>
+      <c r="C48" s="1">
+        <v>372795</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26040" windowHeight="11625"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26025" windowHeight="10155"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$48</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$50</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>12594</v>
+        <v>12239</v>
       </c>
       <c r="C3" s="1">
-        <v>120906</v>
+        <v>117747</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>13660</v>
+        <v>13302</v>
       </c>
       <c r="C4" s="1">
-        <v>135225</v>
+        <v>132055</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>14388</v>
+        <v>14028</v>
       </c>
       <c r="C5" s="1">
-        <v>141797</v>
+        <v>138621</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>14905</v>
+        <v>14544</v>
       </c>
       <c r="C6" s="1">
-        <v>151414</v>
+        <v>148236</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>15364</v>
+        <v>15003</v>
       </c>
       <c r="C7" s="1">
-        <v>156872</v>
+        <v>153694</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>15617</v>
+        <v>15256</v>
       </c>
       <c r="C8" s="1">
-        <v>159889</v>
+        <v>156711</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="3">
-        <v>16034</v>
+        <v>15672</v>
       </c>
       <c r="C9" s="1">
-        <v>165409</v>
+        <v>162227</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="3">
-        <v>16257</v>
+        <v>15895</v>
       </c>
       <c r="C10" s="1">
-        <v>167056</v>
+        <v>163874</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="3">
-        <v>16540</v>
+        <v>16177</v>
       </c>
       <c r="C11" s="1">
-        <v>168750</v>
+        <v>165567</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -510,11 +510,11 @@
       <c r="A12" s="1">
         <v>20200420</v>
       </c>
-      <c r="B12" s="1">
-        <v>16683</v>
+      <c r="B12" s="3">
+        <v>16319</v>
       </c>
       <c r="C12" s="1">
-        <v>170201</v>
+        <v>167014</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -523,11 +523,11 @@
       <c r="A13" s="1">
         <v>20200421</v>
       </c>
-      <c r="B13" s="1">
-        <v>17062</v>
+      <c r="B13" s="3">
+        <v>16698</v>
       </c>
       <c r="C13" s="1">
-        <v>174332</v>
+        <v>171145</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>17362</v>
+        <v>16995</v>
       </c>
       <c r="C14" s="1">
-        <v>177211</v>
+        <v>174002</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>17714</v>
+        <v>17342</v>
       </c>
       <c r="C15" s="1">
-        <v>180507</v>
+        <v>177267</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>17865</v>
+        <v>17492</v>
       </c>
       <c r="C16" s="1">
-        <v>182830</v>
+        <v>179587</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>18064</v>
+        <v>17691</v>
       </c>
       <c r="C17" s="1">
-        <v>184702</v>
+        <v>181459</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>18277</v>
+        <v>17904</v>
       </c>
       <c r="C18" s="1">
-        <v>186460</v>
+        <v>183217</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>18432</v>
+        <v>18059</v>
       </c>
       <c r="C19" s="1">
-        <v>187840</v>
+        <v>184597</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>18648</v>
+        <v>18275</v>
       </c>
       <c r="C20" s="1">
-        <v>190979</v>
+        <v>187736</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>19283</v>
+        <v>18910</v>
       </c>
       <c r="C21" s="1">
-        <v>202855</v>
+        <v>199612</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>20131</v>
+        <v>19754</v>
       </c>
       <c r="C22" s="1">
-        <v>216375</v>
+        <v>213075</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>20963</v>
+        <v>20584</v>
       </c>
       <c r="C23" s="1">
-        <v>228515</v>
+        <v>225192</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>22088</v>
+        <v>21707</v>
       </c>
       <c r="C24" s="1">
-        <v>242037</v>
+        <v>238712</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -679,11 +679,11 @@
       <c r="A25" s="1">
         <v>20200508</v>
       </c>
-      <c r="B25" s="1">
-        <v>22998</v>
+      <c r="B25" s="3">
+        <v>22615</v>
       </c>
       <c r="C25" s="1">
-        <v>251857</v>
+        <v>248525</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>23928</v>
+        <v>23545</v>
       </c>
       <c r="C26" s="1">
-        <v>264243</v>
+        <v>260911</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -705,11 +705,11 @@
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
-      <c r="B27" s="3">
-        <v>24472</v>
+      <c r="B27" s="1">
+        <v>24089</v>
       </c>
       <c r="C27" s="1">
-        <v>272140</v>
+        <v>268808</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="3">
-        <v>25039</v>
+        <v>24655</v>
       </c>
       <c r="C28" s="1">
-        <v>280589</v>
+        <v>277255</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="3">
-        <v>25567</v>
+        <v>25183</v>
       </c>
       <c r="C29" s="1">
-        <v>285801</v>
+        <v>282467</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="3">
-        <v>26001</v>
+        <v>25616</v>
       </c>
       <c r="C30" s="1">
-        <v>300615</v>
+        <v>297279</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -757,11 +757,11 @@
       <c r="A31" s="1">
         <v>20200518</v>
       </c>
-      <c r="B31" s="1">
-        <v>26413</v>
+      <c r="B31" s="3">
+        <v>26027</v>
       </c>
       <c r="C31" s="1">
-        <v>306217</v>
+        <v>302880</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -770,11 +770,11 @@
       <c r="A32" s="1">
         <v>20200519</v>
       </c>
-      <c r="B32" s="1">
-        <v>27014</v>
+      <c r="B32" s="3">
+        <v>26628</v>
       </c>
       <c r="C32" s="1">
-        <v>314795</v>
+        <v>311458</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>27493</v>
+        <v>27107</v>
       </c>
       <c r="C33" s="1">
-        <v>320252</v>
+        <v>316915</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>27937</v>
+        <v>27551</v>
       </c>
       <c r="C34" s="1">
-        <v>324860</v>
+        <v>321523</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>28305</v>
+        <v>27918</v>
       </c>
       <c r="C35" s="1">
-        <v>330255</v>
+        <v>326917</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,10 +823,10 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>28713</v>
+        <v>28325</v>
       </c>
       <c r="C36" s="1">
-        <v>333554</v>
+        <v>330215</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -836,10 +836,10 @@
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>29010</v>
+        <v>28621</v>
       </c>
       <c r="C37" s="1">
-        <v>337053</v>
+        <v>333712</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -849,10 +849,10 @@
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>29633</v>
+        <v>29244</v>
       </c>
       <c r="C38" s="1">
-        <v>343103</v>
+        <v>339762</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -862,10 +862,10 @@
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>29855</v>
+        <v>29466</v>
       </c>
       <c r="C39" s="1">
-        <v>346066</v>
+        <v>342725</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -875,10 +875,10 @@
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>30112</v>
+        <v>29722</v>
       </c>
       <c r="C40" s="1">
-        <v>348928</v>
+        <v>345283</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -888,10 +888,10 @@
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>30336</v>
+        <v>29946</v>
       </c>
       <c r="C41" s="1">
-        <v>354178</v>
+        <v>350533</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -901,10 +901,10 @@
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>30645</v>
+        <v>30255</v>
       </c>
       <c r="C42" s="1">
-        <v>356814</v>
+        <v>353169</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -914,10 +914,10 @@
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>30846</v>
+        <v>30456</v>
       </c>
       <c r="C43" s="1">
-        <v>358956</v>
+        <v>355311</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -927,10 +927,10 @@
         <v>20200608</v>
       </c>
       <c r="B44" s="1">
-        <v>31037</v>
+        <v>30646</v>
       </c>
       <c r="C44" s="1">
-        <v>361176</v>
+        <v>357528</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -940,10 +940,10 @@
         <v>20200609</v>
       </c>
       <c r="B45" s="1">
-        <v>31256</v>
+        <v>30865</v>
       </c>
       <c r="C45" s="1">
-        <v>362881</v>
+        <v>359233</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -953,10 +953,10 @@
         <v>20200610</v>
       </c>
       <c r="B46" s="1">
-        <v>31494</v>
+        <v>31101</v>
       </c>
       <c r="C46" s="1">
-        <v>364835</v>
+        <v>361177</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -966,10 +966,10 @@
         <v>20200611</v>
       </c>
       <c r="B47" s="1">
-        <v>31747</v>
+        <v>31353</v>
       </c>
       <c r="C47" s="1">
-        <v>367746</v>
+        <v>364087</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -979,18 +979,44 @@
         <v>20200612</v>
       </c>
       <c r="B48" s="1">
-        <v>32344</v>
+        <v>31950</v>
       </c>
       <c r="C48" s="1">
-        <v>372795</v>
+        <v>369136</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>20200615</v>
+      </c>
+      <c r="B49" s="1">
+        <v>32226</v>
+      </c>
+      <c r="C49" s="1">
+        <v>373277</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>20200616</v>
+      </c>
+      <c r="B50" s="1">
+        <v>32413</v>
+      </c>
+      <c r="C50" s="1">
+        <v>374955</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26025" windowHeight="10155"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$50</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$55</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>12239</v>
+        <v>11936</v>
       </c>
       <c r="C3" s="1">
-        <v>117747</v>
+        <v>115299</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>13302</v>
+        <v>12997</v>
       </c>
       <c r="C4" s="1">
-        <v>132055</v>
+        <v>129597</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>14028</v>
+        <v>13714</v>
       </c>
       <c r="C5" s="1">
-        <v>138621</v>
+        <v>135541</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>14544</v>
+        <v>14229</v>
       </c>
       <c r="C6" s="1">
-        <v>148236</v>
+        <v>145152</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>15003</v>
+        <v>14687</v>
       </c>
       <c r="C7" s="1">
-        <v>153694</v>
+        <v>150606</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>15256</v>
+        <v>14940</v>
       </c>
       <c r="C8" s="1">
-        <v>156711</v>
+        <v>153623</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="3">
-        <v>15672</v>
+        <v>15355</v>
       </c>
       <c r="C9" s="1">
-        <v>162227</v>
+        <v>159138</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="3">
-        <v>15895</v>
+        <v>15577</v>
       </c>
       <c r="C10" s="1">
-        <v>163874</v>
+        <v>160779</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="3">
-        <v>16177</v>
+        <v>15859</v>
       </c>
       <c r="C11" s="1">
-        <v>165567</v>
+        <v>162472</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="3">
-        <v>16319</v>
+        <v>16001</v>
       </c>
       <c r="C12" s="1">
-        <v>167014</v>
+        <v>163919</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="3">
-        <v>16698</v>
+        <v>16380</v>
       </c>
       <c r="C13" s="1">
-        <v>171145</v>
+        <v>168050</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -537,10 +537,10 @@
         <v>20200422</v>
       </c>
       <c r="B14" s="1">
-        <v>16995</v>
+        <v>16675</v>
       </c>
       <c r="C14" s="1">
-        <v>174002</v>
+        <v>170902</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>17342</v>
+        <v>17022</v>
       </c>
       <c r="C15" s="1">
-        <v>177267</v>
+        <v>174167</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>17492</v>
+        <v>17171</v>
       </c>
       <c r="C16" s="1">
-        <v>179587</v>
+        <v>176292</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>17691</v>
+        <v>17370</v>
       </c>
       <c r="C17" s="1">
-        <v>181459</v>
+        <v>178164</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>17904</v>
+        <v>17580</v>
       </c>
       <c r="C18" s="1">
-        <v>183217</v>
+        <v>179916</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>18059</v>
+        <v>17734</v>
       </c>
       <c r="C19" s="1">
-        <v>184597</v>
+        <v>181295</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>18275</v>
+        <v>17948</v>
       </c>
       <c r="C20" s="1">
-        <v>187736</v>
+        <v>184381</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>18910</v>
+        <v>18581</v>
       </c>
       <c r="C21" s="1">
-        <v>199612</v>
+        <v>196216</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>19754</v>
+        <v>19424</v>
       </c>
       <c r="C22" s="1">
-        <v>213075</v>
+        <v>209677</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>20584</v>
+        <v>20253</v>
       </c>
       <c r="C23" s="1">
-        <v>225192</v>
+        <v>221792</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>21707</v>
+        <v>21374</v>
       </c>
       <c r="C24" s="1">
-        <v>238712</v>
+        <v>235266</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>22615</v>
+        <v>22281</v>
       </c>
       <c r="C25" s="1">
-        <v>248525</v>
+        <v>245076</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>23545</v>
+        <v>23211</v>
       </c>
       <c r="C26" s="1">
-        <v>260911</v>
+        <v>257462</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -706,10 +706,10 @@
         <v>20200512</v>
       </c>
       <c r="B27" s="1">
-        <v>24089</v>
+        <v>23753</v>
       </c>
       <c r="C27" s="1">
-        <v>268808</v>
+        <v>265310</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -719,10 +719,10 @@
         <v>20200513</v>
       </c>
       <c r="B28" s="3">
-        <v>24655</v>
+        <v>24316</v>
       </c>
       <c r="C28" s="1">
-        <v>277255</v>
+        <v>273742</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="3">
-        <v>25183</v>
+        <v>24844</v>
       </c>
       <c r="C29" s="1">
-        <v>282467</v>
+        <v>278954</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="3">
-        <v>25616</v>
+        <v>25275</v>
       </c>
       <c r="C30" s="1">
-        <v>297279</v>
+        <v>293737</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="3">
-        <v>26027</v>
+        <v>25686</v>
       </c>
       <c r="C31" s="1">
-        <v>302880</v>
+        <v>299338</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="3">
-        <v>26628</v>
+        <v>26283</v>
       </c>
       <c r="C32" s="1">
-        <v>311458</v>
+        <v>306453</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -784,10 +784,10 @@
         <v>20200520</v>
       </c>
       <c r="B33" s="1">
-        <v>27107</v>
+        <v>26757</v>
       </c>
       <c r="C33" s="1">
-        <v>316915</v>
+        <v>311803</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>27551</v>
+        <v>27201</v>
       </c>
       <c r="C34" s="1">
-        <v>321523</v>
+        <v>316411</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>27918</v>
+        <v>27566</v>
       </c>
       <c r="C35" s="1">
-        <v>326917</v>
+        <v>321803</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,10 +823,10 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>28325</v>
+        <v>27972</v>
       </c>
       <c r="C36" s="1">
-        <v>330215</v>
+        <v>325050</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -836,10 +836,10 @@
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>28621</v>
+        <v>28267</v>
       </c>
       <c r="C37" s="1">
-        <v>333712</v>
+        <v>328400</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -849,10 +849,10 @@
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>29244</v>
+        <v>28889</v>
       </c>
       <c r="C38" s="1">
-        <v>339762</v>
+        <v>334440</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -862,10 +862,10 @@
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>29466</v>
+        <v>29110</v>
       </c>
       <c r="C39" s="1">
-        <v>342725</v>
+        <v>337401</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -875,10 +875,10 @@
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>29722</v>
+        <v>29366</v>
       </c>
       <c r="C40" s="1">
-        <v>345283</v>
+        <v>339959</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -888,10 +888,10 @@
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>29946</v>
+        <v>29587</v>
       </c>
       <c r="C41" s="1">
-        <v>350533</v>
+        <v>345153</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -901,10 +901,10 @@
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>30255</v>
+        <v>29896</v>
       </c>
       <c r="C42" s="1">
-        <v>353169</v>
+        <v>347789</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -914,10 +914,10 @@
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>30456</v>
+        <v>30097</v>
       </c>
       <c r="C43" s="1">
-        <v>355311</v>
+        <v>349931</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -927,10 +927,10 @@
         <v>20200608</v>
       </c>
       <c r="B44" s="1">
-        <v>30646</v>
+        <v>30286</v>
       </c>
       <c r="C44" s="1">
-        <v>357528</v>
+        <v>352119</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -940,10 +940,10 @@
         <v>20200609</v>
       </c>
       <c r="B45" s="1">
-        <v>30865</v>
+        <v>30504</v>
       </c>
       <c r="C45" s="1">
-        <v>359233</v>
+        <v>353820</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -953,10 +953,10 @@
         <v>20200610</v>
       </c>
       <c r="B46" s="1">
-        <v>31101</v>
+        <v>30740</v>
       </c>
       <c r="C46" s="1">
-        <v>361177</v>
+        <v>355764</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -966,10 +966,10 @@
         <v>20200611</v>
       </c>
       <c r="B47" s="1">
-        <v>31353</v>
+        <v>30992</v>
       </c>
       <c r="C47" s="1">
-        <v>364087</v>
+        <v>358674</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -979,10 +979,10 @@
         <v>20200612</v>
       </c>
       <c r="B48" s="1">
-        <v>31950</v>
+        <v>31582</v>
       </c>
       <c r="C48" s="1">
-        <v>369136</v>
+        <v>363313</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -992,10 +992,10 @@
         <v>20200615</v>
       </c>
       <c r="B49" s="1">
-        <v>32226</v>
+        <v>31858</v>
       </c>
       <c r="C49" s="1">
-        <v>373277</v>
+        <v>367454</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -1005,18 +1005,78 @@
         <v>20200616</v>
       </c>
       <c r="B50" s="1">
-        <v>32413</v>
+        <v>32044</v>
       </c>
       <c r="C50" s="1">
-        <v>374955</v>
+        <v>369130</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
+      <c r="A51" s="1">
+        <v>20200617</v>
+      </c>
+      <c r="B51" s="1">
+        <v>32066</v>
+      </c>
+      <c r="C51" s="1">
+        <v>369382</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>20200618</v>
+      </c>
+      <c r="B52" s="1">
+        <v>32206</v>
+      </c>
+      <c r="C52" s="1">
+        <v>370499</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>20200619</v>
+      </c>
+      <c r="B53" s="1">
+        <v>32302</v>
+      </c>
+      <c r="C53" s="1">
+        <v>371206</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>20200622</v>
+      </c>
+      <c r="B54" s="1">
+        <v>32506</v>
+      </c>
+      <c r="C54" s="1">
+        <v>374748</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>20200623</v>
+      </c>
+      <c r="B55" s="1">
+        <v>32558</v>
+      </c>
+      <c r="C55" s="1">
+        <v>375639</v>
+      </c>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/KAE Voranm KTZH.xlsx
+++ b/KAE Voranm KTZH.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26505" windowHeight="11895"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21225" windowHeight="11595"/>
   </bookViews>
   <sheets>
     <sheet name="KArb VA U AN täglich Kanton ..." sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$55</definedName>
+    <definedName name="MSTR.KArb_VA_U_AN_täglich_Kanton_Zürich">'KArb VA U AN täglich Kanton ...'!$A$1:$C$60</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -363,7 +363,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -394,10 +394,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>11936</v>
+        <v>11886</v>
       </c>
       <c r="C3" s="1">
-        <v>115299</v>
+        <v>114520</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -407,10 +407,10 @@
         <v>20200406</v>
       </c>
       <c r="B4" s="3">
-        <v>12997</v>
+        <v>12943</v>
       </c>
       <c r="C4" s="1">
-        <v>129597</v>
+        <v>128800</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -420,10 +420,10 @@
         <v>20200407</v>
       </c>
       <c r="B5" s="3">
-        <v>13714</v>
+        <v>13659</v>
       </c>
       <c r="C5" s="1">
-        <v>135541</v>
+        <v>134667</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -433,10 +433,10 @@
         <v>20200408</v>
       </c>
       <c r="B6" s="3">
-        <v>14229</v>
+        <v>14172</v>
       </c>
       <c r="C6" s="1">
-        <v>145152</v>
+        <v>144211</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -446,10 +446,10 @@
         <v>20200409</v>
       </c>
       <c r="B7" s="3">
-        <v>14687</v>
+        <v>14630</v>
       </c>
       <c r="C7" s="1">
-        <v>150606</v>
+        <v>149665</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -459,10 +459,10 @@
         <v>20200414</v>
       </c>
       <c r="B8" s="3">
-        <v>14940</v>
+        <v>14882</v>
       </c>
       <c r="C8" s="1">
-        <v>153623</v>
+        <v>152525</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -472,10 +472,10 @@
         <v>20200415</v>
       </c>
       <c r="B9" s="3">
-        <v>15355</v>
+        <v>15297</v>
       </c>
       <c r="C9" s="1">
-        <v>159138</v>
+        <v>158040</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -485,10 +485,10 @@
         <v>20200416</v>
       </c>
       <c r="B10" s="3">
-        <v>15577</v>
+        <v>15518</v>
       </c>
       <c r="C10" s="1">
-        <v>160779</v>
+        <v>159678</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -498,10 +498,10 @@
         <v>20200417</v>
       </c>
       <c r="B11" s="3">
-        <v>15859</v>
+        <v>15800</v>
       </c>
       <c r="C11" s="1">
-        <v>162472</v>
+        <v>161371</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -511,10 +511,10 @@
         <v>20200420</v>
       </c>
       <c r="B12" s="3">
-        <v>16001</v>
+        <v>15942</v>
       </c>
       <c r="C12" s="1">
-        <v>163919</v>
+        <v>162818</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -524,10 +524,10 @@
         <v>20200421</v>
       </c>
       <c r="B13" s="3">
-        <v>16380</v>
+        <v>16321</v>
       </c>
       <c r="C13" s="1">
-        <v>168050</v>
+        <v>166949</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -536,11 +536,11 @@
       <c r="A14" s="1">
         <v>20200422</v>
       </c>
-      <c r="B14" s="1">
-        <v>16675</v>
+      <c r="B14" s="3">
+        <v>16614</v>
       </c>
       <c r="C14" s="1">
-        <v>170902</v>
+        <v>169799</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -550,10 +550,10 @@
         <v>20200423</v>
       </c>
       <c r="B15" s="1">
-        <v>17022</v>
+        <v>16959</v>
       </c>
       <c r="C15" s="1">
-        <v>174167</v>
+        <v>173059</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -563,10 +563,10 @@
         <v>20200424</v>
       </c>
       <c r="B16" s="1">
-        <v>17171</v>
+        <v>17108</v>
       </c>
       <c r="C16" s="1">
-        <v>176292</v>
+        <v>175184</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -576,10 +576,10 @@
         <v>20200427</v>
       </c>
       <c r="B17" s="1">
-        <v>17370</v>
+        <v>17307</v>
       </c>
       <c r="C17" s="1">
-        <v>178164</v>
+        <v>177056</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -589,10 +589,10 @@
         <v>20200428</v>
       </c>
       <c r="B18" s="1">
-        <v>17580</v>
+        <v>17517</v>
       </c>
       <c r="C18" s="1">
-        <v>179916</v>
+        <v>178808</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -602,10 +602,10 @@
         <v>20200429</v>
       </c>
       <c r="B19" s="1">
-        <v>17734</v>
+        <v>17671</v>
       </c>
       <c r="C19" s="1">
-        <v>181295</v>
+        <v>180187</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -615,10 +615,10 @@
         <v>20200430</v>
       </c>
       <c r="B20" s="1">
-        <v>17948</v>
+        <v>17884</v>
       </c>
       <c r="C20" s="1">
-        <v>184381</v>
+        <v>183271</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -628,10 +628,10 @@
         <v>20200504</v>
       </c>
       <c r="B21" s="1">
-        <v>18581</v>
+        <v>18517</v>
       </c>
       <c r="C21" s="1">
-        <v>196216</v>
+        <v>195106</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -641,10 +641,10 @@
         <v>20200505</v>
       </c>
       <c r="B22" s="1">
-        <v>19424</v>
+        <v>19359</v>
       </c>
       <c r="C22" s="1">
-        <v>209677</v>
+        <v>207472</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -654,10 +654,10 @@
         <v>20200506</v>
       </c>
       <c r="B23" s="1">
-        <v>20253</v>
+        <v>20187</v>
       </c>
       <c r="C23" s="1">
-        <v>221792</v>
+        <v>219544</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -667,10 +667,10 @@
         <v>20200507</v>
       </c>
       <c r="B24" s="3">
-        <v>21374</v>
+        <v>21308</v>
       </c>
       <c r="C24" s="1">
-        <v>235266</v>
+        <v>233018</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -680,10 +680,10 @@
         <v>20200508</v>
       </c>
       <c r="B25" s="3">
-        <v>22281</v>
+        <v>22215</v>
       </c>
       <c r="C25" s="1">
-        <v>245076</v>
+        <v>242828</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -693,10 +693,10 @@
         <v>20200511</v>
       </c>
       <c r="B26" s="3">
-        <v>23211</v>
+        <v>23143</v>
       </c>
       <c r="C26" s="1">
-        <v>257462</v>
+        <v>255207</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -705,11 +705,11 @@
       <c r="A27" s="1">
         <v>20200512</v>
       </c>
-      <c r="B27" s="1">
-        <v>23753</v>
+      <c r="B27" s="3">
+        <v>23685</v>
       </c>
       <c r="C27" s="1">
-        <v>265310</v>
+        <v>263055</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -718,11 +718,11 @@
       <c r="A28" s="1">
         <v>20200513</v>
       </c>
-      <c r="B28" s="3">
-        <v>24316</v>
+      <c r="B28" s="1">
+        <v>24248</v>
       </c>
       <c r="C28" s="1">
-        <v>273742</v>
+        <v>271487</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -732,10 +732,10 @@
         <v>20200514</v>
       </c>
       <c r="B29" s="3">
-        <v>24844</v>
+        <v>24774</v>
       </c>
       <c r="C29" s="1">
-        <v>278954</v>
+        <v>276696</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -745,10 +745,10 @@
         <v>20200515</v>
       </c>
       <c r="B30" s="3">
-        <v>25275</v>
+        <v>25205</v>
       </c>
       <c r="C30" s="1">
-        <v>293737</v>
+        <v>291479</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -758,10 +758,10 @@
         <v>20200518</v>
       </c>
       <c r="B31" s="3">
-        <v>25686</v>
+        <v>25616</v>
       </c>
       <c r="C31" s="1">
-        <v>299338</v>
+        <v>297080</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -771,10 +771,10 @@
         <v>20200519</v>
       </c>
       <c r="B32" s="3">
-        <v>26283</v>
+        <v>26213</v>
       </c>
       <c r="C32" s="1">
-        <v>306453</v>
+        <v>304195</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -783,11 +783,11 @@
       <c r="A33" s="1">
         <v>20200520</v>
       </c>
-      <c r="B33" s="1">
-        <v>26757</v>
+      <c r="B33" s="3">
+        <v>26687</v>
       </c>
       <c r="C33" s="1">
-        <v>311803</v>
+        <v>309545</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -797,10 +797,10 @@
         <v>20200522</v>
       </c>
       <c r="B34" s="1">
-        <v>27201</v>
+        <v>27129</v>
       </c>
       <c r="C34" s="1">
-        <v>316411</v>
+        <v>314117</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -810,10 +810,10 @@
         <v>20200525</v>
       </c>
       <c r="B35" s="1">
-        <v>27566</v>
+        <v>27494</v>
       </c>
       <c r="C35" s="1">
-        <v>321803</v>
+        <v>319509</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -823,10 +823,10 @@
         <v>20200526</v>
       </c>
       <c r="B36" s="1">
-        <v>27972</v>
+        <v>27900</v>
       </c>
       <c r="C36" s="1">
-        <v>325050</v>
+        <v>322756</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -836,10 +836,10 @@
         <v>20200527</v>
       </c>
       <c r="B37" s="1">
-        <v>28267</v>
+        <v>28195</v>
       </c>
       <c r="C37" s="1">
-        <v>328400</v>
+        <v>326106</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -849,10 +849,10 @@
         <v>20200528</v>
       </c>
       <c r="B38" s="1">
-        <v>28889</v>
+        <v>28817</v>
       </c>
       <c r="C38" s="1">
-        <v>334440</v>
+        <v>332146</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -862,10 +862,10 @@
         <v>20200529</v>
       </c>
       <c r="B39" s="1">
-        <v>29110</v>
+        <v>29038</v>
       </c>
       <c r="C39" s="1">
-        <v>337401</v>
+        <v>335107</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -875,10 +875,10 @@
         <v>20200602</v>
       </c>
       <c r="B40" s="1">
-        <v>29366</v>
+        <v>29294</v>
       </c>
       <c r="C40" s="1">
-        <v>339959</v>
+        <v>337665</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -888,10 +888,10 @@
         <v>20200603</v>
       </c>
       <c r="B41" s="1">
-        <v>29587</v>
+        <v>29514</v>
       </c>
       <c r="C41" s="1">
-        <v>345153</v>
+        <v>342858</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -901,10 +901,10 @@
         <v>20200604</v>
       </c>
       <c r="B42" s="1">
-        <v>29896</v>
+        <v>29823</v>
       </c>
       <c r="C42" s="1">
-        <v>347789</v>
+        <v>345494</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -914,10 +914,10 @@
         <v>20200605</v>
       </c>
       <c r="B43" s="1">
-        <v>30097</v>
+        <v>30024</v>
       </c>
       <c r="C43" s="1">
-        <v>349931</v>
+        <v>347636</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -927,10 +927,10 @@
         <v>20200608</v>
       </c>
       <c r="B44" s="1">
-        <v>30286</v>
+        <v>30213</v>
       </c>
       <c r="C44" s="1">
-        <v>352119</v>
+        <v>349824</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -940,10 +940,10 @@
         <v>20200609</v>
       </c>
       <c r="B45" s="1">
-        <v>30504</v>
+        <v>30431</v>
       </c>
       <c r="C45" s="1">
-        <v>353820</v>
+        <v>351525</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -953,10 +953,10 @@
         <v>20200610</v>
       </c>
       <c r="B46" s="1">
-        <v>30740</v>
+        <v>30667</v>
       </c>
       <c r="C46" s="1">
-        <v>355764</v>
+        <v>353469</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -966,10 +966,10 @@
         <v>20200611</v>
       </c>
       <c r="B47" s="1">
-        <v>30992</v>
+        <v>30919</v>
       </c>
       <c r="C47" s="1">
-        <v>358674</v>
+        <v>356379</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -979,10 +979,10 @@
         <v>20200612</v>
       </c>
       <c r="B48" s="1">
-        <v>31582</v>
+        <v>31509</v>
       </c>
       <c r="C48" s="1">
-        <v>363313</v>
+        <v>361018</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -992,10 +992,10 @@
         <v>20200615</v>
       </c>
       <c r="B49" s="1">
-        <v>31858</v>
+        <v>31783</v>
       </c>
       <c r="C49" s="1">
-        <v>367454</v>
+        <v>365127</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -1005,10 +1005,10 @@
         <v>20200616</v>
       </c>
       <c r="B50" s="1">
-        <v>32044</v>
+        <v>31968</v>
       </c>
       <c r="C50" s="1">
-        <v>369130</v>
+        <v>366792</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -1018,10 +1018,10 @@
         <v>20200617</v>
       </c>
       <c r="B51" s="1">
-        <v>32066</v>
+        <v>31990</v>
       </c>
       <c r="C51" s="1">
-        <v>369382</v>
+        <v>367044</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -1031,10 +1031,10 @@
         <v>20200618</v>
       </c>
       <c r="B52" s="1">
-        <v>32206</v>
+        <v>32130</v>
       </c>
       <c r="C52" s="1">
-        <v>370499</v>
+        <v>368161</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -1044,10 +1044,10 @@
         <v>20200619</v>
       </c>
       <c r="B53" s="1">
-        <v>32302</v>
+        <v>32226</v>
       </c>
       <c r="C53" s="1">
-        <v>371206</v>
+        <v>368868</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -1057,10 +1057,10 @@
         <v>20200622</v>
       </c>
       <c r="B54" s="1">
-        <v>32506</v>
+        <v>32430</v>
       </c>
       <c r="C54" s="1">
-        <v>374748</v>
+        <v>372410</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -1070,13 +1070,78 @@
         <v>20200623</v>
       </c>
       <c r="B55" s="1">
-        <v>32558</v>
+        <v>32480</v>
       </c>
       <c r="C55" s="1">
-        <v>375639</v>
+        <v>373297</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>20200624</v>
+      </c>
+      <c r="B56" s="1">
+        <v>32509</v>
+      </c>
+      <c r="C56" s="1">
+        <v>373521</v>
+      </c>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>20200625</v>
+      </c>
+      <c r="B57" s="1">
+        <v>32540</v>
+      </c>
+      <c r="C57" s="1">
+        <v>374066</v>
+      </c>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>20200626</v>
+      </c>
+      <c r="B58" s="1">
+        <v>32567</v>
+      </c>
+      <c r="C58" s="1">
+        <v>374976</v>
+      </c>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>20200629</v>
+      </c>
+      <c r="B59" s="1">
+        <v>32597</v>
+      </c>
+      <c r="C59" s="1">
+        <v>375263</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>20200630</v>
+      </c>
+      <c r="B60" s="1">
+        <v>32629</v>
+      </c>
+      <c r="C60" s="1">
+        <v>376573</v>
+      </c>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
